--- a/Proyecto Final ADA-PCD Pruebas.xlsx
+++ b/Proyecto Final ADA-PCD Pruebas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University\ada\Proyecto-ADA-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212AEF20-23B8-4B68-BBDD-EB4B146E7DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFCEAB5-B9E2-4AB6-923A-652802969269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14880" yWindow="840" windowWidth="21375" windowHeight="19425" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plantilla" sheetId="14" r:id="rId1"/>
@@ -20,8 +20,9 @@
     <sheet name="15 Elementos" sheetId="15" r:id="rId5"/>
     <sheet name="20 Elementos" sheetId="16" r:id="rId6"/>
     <sheet name="21 Elementos" sheetId="17" r:id="rId7"/>
-    <sheet name="Resumen" sheetId="18" r:id="rId8"/>
-    <sheet name="Especificaciones" sheetId="7" r:id="rId9"/>
+    <sheet name="Limites de CUDA" sheetId="19" r:id="rId8"/>
+    <sheet name="Resumen" sheetId="18" r:id="rId9"/>
+    <sheet name="Especificaciones" sheetId="7" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,14 +38,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="oNDZ1K2ok2dz+6TLejnorV9AwdEzTjVu/G6dSvSVqng="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="oNDZ1K2ok2dz+6TLejnorV9AwdEzTjVu/G6dSvSVqng="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="771">
   <si>
     <t>Subsistema</t>
   </si>
@@ -2828,17 +2829,295 @@
   </si>
   <si>
     <t>SpeedUp (x)</t>
+  </si>
+  <si>
+    <t>Perdida</t>
+  </si>
+  <si>
+    <t>Tiempo</t>
+  </si>
+  <si>
+    <t>LIMITES DE GEOMETRIC CUDA</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTU_{t+1}|ABCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTU_{t+1}|ABCDEFGHIJKLMNOPQRST_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTU_{t+1}|BCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTU_{t+1}|BCDEFGHIJKLMNOPQRST_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTU_{t+1}|ACEGIKMOQSU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTU_{t+1}|BDFHJLNPRT_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTU_{t+1}|ABDEGHIJKLMNOPQSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRST_{t+1}|ABCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRST_{t+1}|BCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRST_{t+1}|ACEGIKMOQSU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRST_{t+1}|ABDEGHIJKLMNOPQSTU_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRSTU_{t+1}|ABCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRSTU_{t+1}|ABCDEFGHIJKLMNOPQRST_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRSTU_{t+1}|BCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRSTU_{t+1}|BCDEFGHIJKLMNOPQRST_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRSTU_{t+1}|ACEGIKMOQSU_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRSTU_{t+1}|BDFHJLNPRT_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRSTU_{t+1}|ABDEGHIJKLMNOPQSTU_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRST_{t+1}|ABCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRST_{t+1}|BCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRST_{t+1}|ACEGIKMOQSU_{t}</t>
+  </si>
+  <si>
+    <t>BCDEFGHIJKLMNOPQRST_{t+1}|ABDEGHIJKLMNOPQSTU_{t}</t>
+  </si>
+  <si>
+    <t>ACEGIKMOQSU_{t+1}|ABCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>ACEGIKMOQSU_{t+1}|ABCDEFGHIJKLMNOPQRST_{t}</t>
+  </si>
+  <si>
+    <t>ACEGIKMOQSU_{t+1}|BCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>ACEGIKMOQSU_{t+1}|BCDEFGHIJKLMNOPQRST_{t}</t>
+  </si>
+  <si>
+    <t>ACEGIKMOQSU_{t+1}|ACEGIKMOQSU_{t}</t>
+  </si>
+  <si>
+    <t>ACEGIKMOQSU_{t+1}|BDFHJLNPRT_{t}</t>
+  </si>
+  <si>
+    <t>ACEGIKMOQSU_{t+1}|ABDEGHIJKLMNOPQSTU_{t}</t>
+  </si>
+  <si>
+    <t>BDFHJLNPRT_{t+1}|ABCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>BDFHJLNPRT_{t+1}|BCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>BDFHJLNPRT_{t+1}|ACEGIKMOQSU_{t}</t>
+  </si>
+  <si>
+    <t>BDFHJLNPRT_{t+1}|ABDEGHIJKLMNOPQSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABDEGHIJKLMNOPQSTU_{t+1}|ABCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABDEGHIJKLMNOPQSTU_{t+1}|ABCDEFGHIJKLMNOPQRST_{t}</t>
+  </si>
+  <si>
+    <t>ABDEGHIJKLMNOPQSTU_{t+1}|BCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABDEGHIJKLMNOPQSTU_{t+1}|BCDEFGHIJKLMNOPQRST_{t}</t>
+  </si>
+  <si>
+    <t>ABDEGHIJKLMNOPQSTU_{t+1}|ACEGIKMOQSU_{t}</t>
+  </si>
+  <si>
+    <t>ABDEGHIJKLMNOPQSTU_{t+1}|BDFHJLNPRT_{t}</t>
+  </si>
+  <si>
+    <t>ABDEGHIJKLMNOPQSTU_{t+1}|ABDEGHIJKLMNOPQSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUV_{t+1}|ABCDEFGHIJKLMNOPQRSTUV_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUV_{t+1}|ABCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUV_{t+1}|BCDEFGHIJKLMNOPQRSTUV_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUV_{t+1}|BCDEFGHIJKLMNOPQRSTU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUV_{t+1}|ACEGIKMOQSV_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUV_{t+1}|BDFHJLNPRTU_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUV_{t+1}|ABDEGHIJKLMNOPQRSTUV_{t}</t>
+  </si>
+  <si>
+    <t>22N</t>
+  </si>
+  <si>
+    <t>23N</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUVW_{t+1}|ABCDEFGHIJKLMNOPQRSTUVW_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUVW_{t+1}|ABCDEFGHIJKLMNOPQRSTUV_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUVW_{t+1}|BCDEFGHIJKLMNOPQRSTUVW_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUVW_{t+1}|BCDEFGHIJKLMNOPQRSTUV_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUVW_{t+1}|ACEGIKMOQSUW_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUVW_{t+1}|BDFHJLNPRTV_{t}</t>
+  </si>
+  <si>
+    <t>ABCDEFGHIJKLMNOPQRSTUVW_{t+1}|ABDEGHIJKLMNOPQRSTUW_{t}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ S ⎞⎛  A,B,C,D,E,F,G,H,I,J,K,L,M,N,O,P,Q,R,T,U,V  ⎞_x000D_
+⎝ ∅ ⎠⎝ a,b,c,d,e,f,g,h,i,j,k,l,m,n,o,p,q,r,s,t,u,v ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ C ⎞⎛ A,B,D,E,F,G,H,I,J,K,L,M,N,O,P,Q,R,S,T,U,V ⎞_x000D_
+⎝ ∅ ⎠⎝ a,b,c,d,e,f,g,h,i,j,k,l,m,n,o,p,q,r,s,t,u ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ B ⎞⎛ A,C,D,E,F,G,H,I,J,K,L,M,N,O,P,Q,R,S,T,U,V ⎞_x000D_
+⎝ ∅ ⎠⎝ b,c,d,e,f,g,h,i,j,k,l,m,n,o,p,q,r,s,t,u,v ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ U ⎞⎛ A,B,C,D,E,F,G,H,I,J,K,L,M,N,O,P,Q,R,S,T,V ⎞_x000D_
+⎝ ∅ ⎠⎝  b,c,d,e,f,g,h,i,j,k,l,m,n,o,p,q,r,s,t,u  ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ T ⎞⎛ A,B,C,D,E,F,G,H,I,J,K,L,M,N,O,P,Q,R,S,U,V ⎞_x000D_
+⎝ ∅ ⎠⎝           a,c,e,g,i,k,m,o,q,s,u           ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ Q ⎞⎛ A,B,C,D,E,F,G,H,I,J,K,L,M,N,O,P,R,S,T,U,V ⎞_x000D_
+⎝ ∅ ⎠⎝       a,b,d,e,g,h,j,k,m,n,p,q,s,t,v       ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ C ⎞⎛ A,B,D,E,F,G,H,I,J,K,L,M,N,O,P,Q,R,S,T,U,V ⎞
+⎝ ∅ ⎠⎝           b,d,f,h,j,l,n,p,r,t,v           ⎠
+</t>
+  </si>
+  <si>
+    <t>Funcion</t>
+  </si>
+  <si>
+    <t>Nota 1</t>
+  </si>
+  <si>
+    <t>Nota 2</t>
+  </si>
+  <si>
+    <t>Solo CUDA</t>
+  </si>
+  <si>
+    <t>CUDA + MP</t>
+  </si>
+  <si>
+    <t>COSTOS POR FUNCION - CUDA</t>
+  </si>
+  <si>
+    <t>Para estas biparticiones se utilizo CUDA con el resto de funciones en secuencial</t>
+  </si>
+  <si>
+    <t>Para estas biparticiones se utilizo CUDA con la funcion 3 Paralelizada con MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ Q ⎞⎛  A,B,C,D,E,F,G,H,I,J,K,L,M,N,O,P,R,S,T,U,V,W  ⎞_x000D_
+⎝ ∅ ⎠⎝ a,b,c,d,e,f,g,h,i,j,k,l,m,n,o,p,q,r,s,t,u,v,w ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ H ⎞⎛ A,B,C,D,E,F,G,I,J,K,L,M,N,O,P,Q,R,S,T,U,V,W ⎞_x000D_
+⎝ ∅ ⎠⎝ a,b,c,d,e,f,g,h,i,j,k,l,m,n,o,p,q,r,s,t,u,v ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ J ⎞⎛ A,B,C,D,E,F,G,H,I,K,L,M,N,O,P,Q,R,S,T,U,V,W ⎞_x000D_
+⎝ ∅ ⎠⎝ b,c,d,e,f,g,h,i,j,k,l,m,n,o,p,q,r,s,t,u,v,w ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ J ⎞⎛ A,B,C,D,E,F,G,H,I,K,L,M,N,O,P,Q,R,S,T,U,V,W ⎞_x000D_
+⎝ ∅ ⎠⎝  b,c,d,e,f,g,h,i,j,k,l,m,n,o,p,q,r,s,t,u,v  ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ F ⎞⎛ A,B,C,D,E,G,H,I,J,K,L,M,N,O,P,Q,R,S,T,U,V,W ⎞_x000D_
+⎝ ∅ ⎠⎝           a,c,e,g,i,k,m,o,q,s,u,w           ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ F ⎞⎛ A,B,C,D,E,G,H,I,J,K,L,M,N,O,P,Q,R,S,T,U,V,W ⎞_x000D_
+⎝ ∅ ⎠⎝            b,d,f,h,j,l,n,p,r,t,v            ⎠_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⎛ B ⎞⎛ A,C,D,E,F,G,H,I,J,K,L,M,N,O,P,Q,R,S,T,U,V,W ⎞_x000D_
+⎝ ∅ ⎠⎝       a,b,d,e,g,h,j,k,m,n,p,q,s,t,v,w       ⎠_x000D_
+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2935,7 +3214,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3029,6 +3308,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3245,12 +3536,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3260,43 +3551,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3305,7 +3596,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3314,70 +3605,70 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3386,46 +3677,46 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3440,7 +3731,7 @@
     <xf numFmtId="10" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3455,10 +3746,10 @@
     <xf numFmtId="2" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3470,212 +3761,297 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -35980,44 +36356,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="125" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="85" t="s">
+      <c r="B1" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="126" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="86" t="s">
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="127" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="87" t="s">
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="128" t="s">
         <v>525</v>
       </c>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="88" t="s">
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="129" t="s">
         <v>575</v>
       </c>
-      <c r="M1" s="89"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="91" t="s">
+      <c r="M1" s="130"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="132" t="s">
         <v>210</v>
       </c>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="92"/>
-      <c r="T1" s="93"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="134"/>
     </row>
     <row r="2" spans="1:20" ht="31.5">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
       <c r="C2" s="13" t="s">
         <v>1</v>
       </c>
@@ -38174,11 +38550,11 @@
       </c>
     </row>
     <row r="53" spans="1:20" ht="18.75">
-      <c r="I53" s="94" t="s">
+      <c r="I53" s="135" t="s">
         <v>370</v>
       </c>
-      <c r="J53" s="94"/>
-      <c r="K53" s="94"/>
+      <c r="J53" s="135"/>
+      <c r="K53" s="135"/>
       <c r="L53" s="26"/>
       <c r="M53" s="45"/>
       <c r="N53" s="45"/>
@@ -38208,11 +38584,11 @@
       </c>
     </row>
     <row r="54" spans="1:20" ht="18.75">
-      <c r="I54" s="95" t="s">
+      <c r="I54" s="136" t="s">
         <v>371</v>
       </c>
-      <c r="J54" s="95"/>
-      <c r="K54" s="95"/>
+      <c r="J54" s="136"/>
+      <c r="K54" s="136"/>
       <c r="L54" s="27"/>
       <c r="M54" s="46"/>
       <c r="N54" s="46"/>
@@ -38242,11 +38618,11 @@
       </c>
     </row>
     <row r="55" spans="1:20" ht="18.75">
-      <c r="I55" s="96" t="s">
+      <c r="I55" s="137" t="s">
         <v>372</v>
       </c>
-      <c r="J55" s="96"/>
-      <c r="K55" s="96"/>
+      <c r="J55" s="137"/>
+      <c r="K55" s="137"/>
       <c r="L55" s="28"/>
       <c r="M55" s="47"/>
       <c r="N55" s="47"/>
@@ -38349,6 +38725,243 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3442CB58-E47F-4D67-9128-0E093C9B1AEB}">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="27" customHeight="1">
+      <c r="A1" s="182" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75">
+      <c r="A2" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75">
+      <c r="A3" s="3"/>
+      <c r="B3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75">
+      <c r="A8" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1167201-5056-4598-B6C2-CCF66112F4A3}">
   <dimension ref="A1:O55"/>
@@ -38371,37 +38984,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="125" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="85" t="s">
+      <c r="B1" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="126" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="86" t="s">
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="127" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="87" t="s">
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="128" t="s">
         <v>525</v>
       </c>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="91" t="s">
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="132" t="s">
         <v>210</v>
       </c>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
     </row>
     <row r="2" spans="1:15" ht="31.5">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
       <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
@@ -40942,11 +41555,11 @@
       </c>
     </row>
     <row r="52" spans="1:15" ht="18.75">
-      <c r="I52" s="94" t="s">
+      <c r="I52" s="135" t="s">
         <v>370</v>
       </c>
-      <c r="J52" s="94"/>
-      <c r="K52" s="94"/>
+      <c r="J52" s="135"/>
+      <c r="K52" s="135"/>
       <c r="L52" s="18">
         <f>AVERAGE(L$3:L$51)</f>
         <v>7.6530612244897961E-2</v>
@@ -40965,11 +41578,11 @@
       </c>
     </row>
     <row r="53" spans="1:15" ht="18.75">
-      <c r="I53" s="95" t="s">
+      <c r="I53" s="136" t="s">
         <v>371</v>
       </c>
-      <c r="J53" s="95"/>
-      <c r="K53" s="95"/>
+      <c r="J53" s="136"/>
+      <c r="K53" s="136"/>
       <c r="L53" s="14">
         <f>MIN(L$3:L$51)</f>
         <v>0</v>
@@ -40988,11 +41601,11 @@
       </c>
     </row>
     <row r="54" spans="1:15" ht="18.75">
-      <c r="I54" s="96" t="s">
+      <c r="I54" s="137" t="s">
         <v>372</v>
       </c>
-      <c r="J54" s="96"/>
-      <c r="K54" s="96"/>
+      <c r="J54" s="137"/>
+      <c r="K54" s="137"/>
       <c r="L54" s="16">
         <f>MAX(L$3:L$51)</f>
         <v>0.25</v>
@@ -41108,6 +41721,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N3:N51">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="N2:O2">
     <cfRule type="colorScale" priority="17">
       <colorScale>
@@ -41134,18 +41759,6 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="N56:O1048576 N3:O51">
     <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N51">
-    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -41196,37 +41809,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="125" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="85" t="s">
+      <c r="B1" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="126" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="86" t="s">
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="127" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="87" t="s">
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="128" t="s">
         <v>525</v>
       </c>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="91" t="s">
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="132" t="s">
         <v>210</v>
       </c>
-      <c r="M1" s="92"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="138"/>
+      <c r="O1" s="138"/>
     </row>
     <row r="2" spans="1:15" ht="31.5">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
       <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
@@ -43768,11 +44381,11 @@
       </c>
     </row>
     <row r="52" spans="1:15" ht="18.75">
-      <c r="I52" s="94" t="s">
+      <c r="I52" s="135" t="s">
         <v>370</v>
       </c>
-      <c r="J52" s="98"/>
-      <c r="K52" s="98"/>
+      <c r="J52" s="139"/>
+      <c r="K52" s="139"/>
       <c r="L52" s="18">
         <f>AVERAGE(L$3:L$51)</f>
         <v>1.7959183673469388E-2</v>
@@ -43791,11 +44404,11 @@
       </c>
     </row>
     <row r="53" spans="1:15" ht="18.75">
-      <c r="I53" s="95" t="s">
+      <c r="I53" s="136" t="s">
         <v>371</v>
       </c>
-      <c r="J53" s="99"/>
-      <c r="K53" s="99"/>
+      <c r="J53" s="140"/>
+      <c r="K53" s="140"/>
       <c r="L53" s="14">
         <f>MIN(L$3:L$51)</f>
         <v>0</v>
@@ -43814,11 +44427,11 @@
       </c>
     </row>
     <row r="54" spans="1:15" ht="18.75">
-      <c r="I54" s="96" t="s">
+      <c r="I54" s="137" t="s">
         <v>372</v>
       </c>
-      <c r="J54" s="100"/>
-      <c r="K54" s="100"/>
+      <c r="J54" s="141"/>
+      <c r="K54" s="141"/>
       <c r="L54" s="16">
         <f>MAX(L$3:L$51)</f>
         <v>0.5</v>
@@ -43934,6 +44547,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N3:N51">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="N2:O2">
     <cfRule type="colorScale" priority="23">
       <colorScale>
@@ -43960,18 +44585,6 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="N56:O1048576 N3:O51">
     <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N51">
-    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -44023,37 +44636,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="125" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="85" t="s">
+      <c r="B1" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="126" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="86" t="s">
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="127" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="87" t="s">
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="128" t="s">
         <v>525</v>
       </c>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="91" t="s">
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="132" t="s">
         <v>210</v>
       </c>
-      <c r="M1" s="92"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="138"/>
+      <c r="O1" s="138"/>
     </row>
     <row r="2" spans="1:15" ht="31.5">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
       <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
@@ -46595,11 +47208,11 @@
       </c>
     </row>
     <row r="52" spans="1:15" ht="18.75">
-      <c r="I52" s="94" t="s">
+      <c r="I52" s="135" t="s">
         <v>370</v>
       </c>
-      <c r="J52" s="98"/>
-      <c r="K52" s="98"/>
+      <c r="J52" s="139"/>
+      <c r="K52" s="139"/>
       <c r="L52" s="18">
         <f>AVERAGE(L$3:L$51)</f>
         <v>4.251700680272113E-4</v>
@@ -46618,11 +47231,11 @@
       </c>
     </row>
     <row r="53" spans="1:15" ht="18.75">
-      <c r="I53" s="95" t="s">
+      <c r="I53" s="136" t="s">
         <v>371</v>
       </c>
-      <c r="J53" s="99"/>
-      <c r="K53" s="99"/>
+      <c r="J53" s="140"/>
+      <c r="K53" s="140"/>
       <c r="L53" s="14">
         <f>MIN(L$3:L$51)</f>
         <v>0</v>
@@ -46641,11 +47254,11 @@
       </c>
     </row>
     <row r="54" spans="1:15" ht="18.75">
-      <c r="I54" s="96" t="s">
+      <c r="I54" s="137" t="s">
         <v>372</v>
       </c>
-      <c r="J54" s="100"/>
-      <c r="K54" s="100"/>
+      <c r="J54" s="141"/>
+      <c r="K54" s="141"/>
       <c r="L54" s="16">
         <f>MAX(L$3:L$51)</f>
         <v>2.0833333333333353E-2</v>
@@ -46761,6 +47374,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N3:N51">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="N2:O2">
     <cfRule type="colorScale" priority="31">
       <colorScale>
@@ -46809,18 +47434,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N51">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -46853,44 +47466,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="125" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="85" t="s">
+      <c r="B1" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="126" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="86" t="s">
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="127" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="87" t="s">
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="128" t="s">
         <v>525</v>
       </c>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="88" t="s">
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="129" t="s">
         <v>575</v>
       </c>
-      <c r="M1" s="104"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="91" t="s">
+      <c r="M1" s="145"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="132" t="s">
         <v>210</v>
       </c>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="106"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="138"/>
+      <c r="S1" s="138"/>
+      <c r="T1" s="147"/>
     </row>
     <row r="2" spans="1:20" ht="31.5">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
       <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
@@ -50231,11 +50844,11 @@
       </c>
     </row>
     <row r="52" spans="1:20" ht="18.75">
-      <c r="I52" s="94" t="s">
+      <c r="I52" s="135" t="s">
         <v>370</v>
       </c>
-      <c r="J52" s="98"/>
-      <c r="K52" s="98"/>
+      <c r="J52" s="139"/>
+      <c r="K52" s="139"/>
       <c r="L52" s="29"/>
       <c r="M52" s="45"/>
       <c r="N52" s="45"/>
@@ -50265,11 +50878,11 @@
       </c>
     </row>
     <row r="53" spans="1:20" ht="18.75">
-      <c r="I53" s="95" t="s">
+      <c r="I53" s="136" t="s">
         <v>371</v>
       </c>
-      <c r="J53" s="99"/>
-      <c r="K53" s="99"/>
+      <c r="J53" s="140"/>
+      <c r="K53" s="140"/>
       <c r="L53" s="30"/>
       <c r="M53" s="46"/>
       <c r="N53" s="46"/>
@@ -50299,11 +50912,11 @@
       </c>
     </row>
     <row r="54" spans="1:20" ht="18.75">
-      <c r="I54" s="96" t="s">
+      <c r="I54" s="137" t="s">
         <v>372</v>
       </c>
-      <c r="J54" s="100"/>
-      <c r="K54" s="100"/>
+      <c r="J54" s="141"/>
+      <c r="K54" s="141"/>
       <c r="L54" s="31"/>
       <c r="M54" s="47"/>
       <c r="N54" s="47"/>
@@ -50449,6 +51062,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R3:R51">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R2:T2">
     <cfRule type="colorScale" priority="9">
       <colorScale>
@@ -50485,18 +51110,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T3:T51">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="S3:S51">
     <cfRule type="colorScale" priority="3">
       <colorScale>
@@ -50509,8 +51122,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R51">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="T3:T51">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -50556,46 +51169,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.75">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="125" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="85" t="s">
+      <c r="B1" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="126" t="s">
         <v>178</v>
       </c>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="86" t="s">
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="127" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="87" t="s">
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="128" t="s">
         <v>525</v>
       </c>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="88" t="s">
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="129" t="s">
         <v>575</v>
       </c>
-      <c r="M1" s="89"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="115" t="s">
+      <c r="M1" s="130"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="148" t="s">
         <v>210</v>
       </c>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
     </row>
     <row r="2" spans="1:22" ht="31.5">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
       <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
@@ -50641,19 +51254,19 @@
       <c r="Q2" s="36" t="s">
         <v>578</v>
       </c>
-      <c r="R2" s="117" t="s">
+      <c r="R2" s="86" t="s">
         <v>290</v>
       </c>
-      <c r="S2" s="118" t="s">
+      <c r="S2" s="87" t="s">
         <v>529</v>
       </c>
-      <c r="T2" s="118" t="s">
+      <c r="T2" s="87" t="s">
         <v>632</v>
       </c>
-      <c r="U2" s="119" t="s">
+      <c r="U2" s="88" t="s">
         <v>579</v>
       </c>
-      <c r="V2" s="114" t="s">
+      <c r="V2" s="85" t="s">
         <v>633</v>
       </c>
     </row>
@@ -50661,7 +51274,7 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="106" t="s">
         <v>40</v>
       </c>
       <c r="C3" s="21" t="s">
@@ -53164,18 +53777,18 @@
         <f t="shared" si="5"/>
         <v>-5.2</v>
       </c>
-      <c r="X35" s="143"/>
-      <c r="Y35" s="143"/>
-      <c r="Z35" s="143"/>
-      <c r="AA35" s="143"/>
-      <c r="AB35" s="143"/>
-      <c r="AC35" s="143"/>
-      <c r="AD35" s="143"/>
-      <c r="AE35" s="143"/>
-      <c r="AF35" s="143"/>
-      <c r="AG35" s="143"/>
-      <c r="AH35" s="143"/>
-      <c r="AI35" s="143"/>
+      <c r="X35" s="102"/>
+      <c r="Y35" s="102"/>
+      <c r="Z35" s="102"/>
+      <c r="AA35" s="102"/>
+      <c r="AB35" s="102"/>
+      <c r="AC35" s="102"/>
+      <c r="AD35" s="102"/>
+      <c r="AE35" s="102"/>
+      <c r="AF35" s="102"/>
+      <c r="AG35" s="102"/>
+      <c r="AH35" s="102"/>
+      <c r="AI35" s="102"/>
     </row>
     <row r="36" spans="1:35" ht="30.75" customHeight="1">
       <c r="A36" s="7">
@@ -53252,20 +53865,20 @@
         <f t="shared" si="5"/>
         <v>-3.83</v>
       </c>
-      <c r="X36" s="143"/>
-      <c r="Y36" s="146" t="s">
+      <c r="X36" s="102"/>
+      <c r="Y36" s="153" t="s">
         <v>688</v>
       </c>
-      <c r="Z36" s="146"/>
-      <c r="AA36" s="146"/>
-      <c r="AB36" s="146"/>
-      <c r="AC36" s="146"/>
-      <c r="AD36" s="146"/>
-      <c r="AE36" s="146"/>
-      <c r="AF36" s="146"/>
-      <c r="AG36" s="146"/>
-      <c r="AH36" s="143"/>
-      <c r="AI36" s="143"/>
+      <c r="Z36" s="153"/>
+      <c r="AA36" s="153"/>
+      <c r="AB36" s="153"/>
+      <c r="AC36" s="153"/>
+      <c r="AD36" s="153"/>
+      <c r="AE36" s="153"/>
+      <c r="AF36" s="153"/>
+      <c r="AG36" s="153"/>
+      <c r="AH36" s="102"/>
+      <c r="AI36" s="102"/>
     </row>
     <row r="37" spans="1:35" ht="30.75" customHeight="1">
       <c r="A37" s="7">
@@ -53342,26 +53955,26 @@
         <f t="shared" si="5"/>
         <v>-1.63</v>
       </c>
-      <c r="X37" s="142"/>
-      <c r="Y37" s="148" t="s">
+      <c r="X37" s="101"/>
+      <c r="Y37" s="160" t="s">
         <v>687</v>
       </c>
-      <c r="Z37" s="148"/>
-      <c r="AA37" s="126" t="s">
+      <c r="Z37" s="160"/>
+      <c r="AA37" s="157" t="s">
         <v>686</v>
       </c>
-      <c r="AB37" s="126"/>
-      <c r="AC37" s="141" t="s">
+      <c r="AB37" s="157"/>
+      <c r="AC37" s="158" t="s">
         <v>685</v>
       </c>
-      <c r="AD37" s="141"/>
-      <c r="AE37" s="129" t="s">
+      <c r="AD37" s="158"/>
+      <c r="AE37" s="159" t="s">
         <v>684</v>
       </c>
-      <c r="AF37" s="129"/>
-      <c r="AG37" s="129"/>
-      <c r="AH37" s="144"/>
-      <c r="AI37" s="144"/>
+      <c r="AF37" s="159"/>
+      <c r="AG37" s="159"/>
+      <c r="AH37" s="103"/>
+      <c r="AI37" s="103"/>
     </row>
     <row r="38" spans="1:35" ht="30.75" customHeight="1">
       <c r="A38" s="7">
@@ -53438,30 +54051,30 @@
         <f t="shared" si="5"/>
         <v>30.33</v>
       </c>
-      <c r="X38" s="122"/>
+      <c r="X38" s="91"/>
       <c r="Y38" s="150">
         <f>E3</f>
         <v>1083.5999999999999</v>
       </c>
       <c r="Z38" s="151"/>
-      <c r="AA38" s="152">
+      <c r="AA38" s="154">
         <f>H3</f>
         <v>413.19</v>
       </c>
-      <c r="AB38" s="153"/>
-      <c r="AC38" s="152">
+      <c r="AB38" s="155"/>
+      <c r="AC38" s="154">
         <f>K3</f>
         <v>88.44</v>
       </c>
-      <c r="AD38" s="153"/>
-      <c r="AE38" s="152">
+      <c r="AD38" s="155"/>
+      <c r="AE38" s="154">
         <f>N3</f>
         <v>22.07</v>
       </c>
-      <c r="AF38" s="153"/>
-      <c r="AG38" s="153"/>
-      <c r="AH38" s="145"/>
-      <c r="AI38" s="145"/>
+      <c r="AF38" s="155"/>
+      <c r="AG38" s="155"/>
+      <c r="AH38" s="104"/>
+      <c r="AI38" s="104"/>
     </row>
     <row r="39" spans="1:35" ht="30.75" customHeight="1">
       <c r="A39" s="7">
@@ -53538,29 +54151,29 @@
         <f t="shared" si="5"/>
         <v>7.07</v>
       </c>
-      <c r="X39" s="140"/>
-      <c r="Y39" s="149" t="s">
+      <c r="X39" s="100"/>
+      <c r="Y39" s="152" t="s">
         <v>689</v>
       </c>
-      <c r="Z39" s="149"/>
-      <c r="AA39" s="147">
+      <c r="Z39" s="152"/>
+      <c r="AA39" s="156">
         <f>$Y$38/AA38</f>
         <v>2.6225223262905684</v>
       </c>
-      <c r="AB39" s="147"/>
-      <c r="AC39" s="147">
+      <c r="AB39" s="156"/>
+      <c r="AC39" s="156">
         <f>$Y$38/AC38</f>
         <v>12.252374491180461</v>
       </c>
-      <c r="AD39" s="147"/>
-      <c r="AE39" s="147">
+      <c r="AD39" s="156"/>
+      <c r="AE39" s="156">
         <f>$Y$38/AE38</f>
         <v>49.098323516085181</v>
       </c>
-      <c r="AF39" s="147"/>
-      <c r="AG39" s="147"/>
-      <c r="AH39" s="140"/>
-      <c r="AI39" s="140"/>
+      <c r="AF39" s="156"/>
+      <c r="AG39" s="156"/>
+      <c r="AH39" s="100"/>
+      <c r="AI39" s="100"/>
     </row>
     <row r="40" spans="1:35" ht="30.75" customHeight="1">
       <c r="A40" s="7">
@@ -53637,18 +54250,18 @@
         <f t="shared" si="5"/>
         <v>12.34</v>
       </c>
-      <c r="X40" s="140"/>
-      <c r="Y40" s="140"/>
-      <c r="Z40" s="140"/>
-      <c r="AA40" s="140"/>
-      <c r="AB40" s="140"/>
-      <c r="AC40" s="140"/>
-      <c r="AD40" s="140"/>
-      <c r="AE40" s="140"/>
-      <c r="AF40" s="140"/>
-      <c r="AG40" s="140"/>
-      <c r="AH40" s="140"/>
-      <c r="AI40" s="140"/>
+      <c r="X40" s="100"/>
+      <c r="Y40" s="100"/>
+      <c r="Z40" s="100"/>
+      <c r="AA40" s="100"/>
+      <c r="AB40" s="100"/>
+      <c r="AC40" s="100"/>
+      <c r="AD40" s="100"/>
+      <c r="AE40" s="100"/>
+      <c r="AF40" s="100"/>
+      <c r="AG40" s="100"/>
+      <c r="AH40" s="100"/>
+      <c r="AI40" s="100"/>
     </row>
     <row r="41" spans="1:35" ht="30.75" customHeight="1">
       <c r="A41" s="7">
@@ -53725,18 +54338,18 @@
         <f t="shared" si="5"/>
         <v>5.53</v>
       </c>
-      <c r="X41" s="140"/>
-      <c r="Y41" s="140"/>
-      <c r="Z41" s="140"/>
-      <c r="AA41" s="140"/>
-      <c r="AB41" s="140"/>
-      <c r="AC41" s="140"/>
-      <c r="AD41" s="140"/>
-      <c r="AE41" s="140"/>
-      <c r="AF41" s="140"/>
-      <c r="AG41" s="140"/>
-      <c r="AH41" s="140"/>
-      <c r="AI41" s="140"/>
+      <c r="X41" s="100"/>
+      <c r="Y41" s="100"/>
+      <c r="Z41" s="100"/>
+      <c r="AA41" s="100"/>
+      <c r="AB41" s="100"/>
+      <c r="AC41" s="100"/>
+      <c r="AD41" s="100"/>
+      <c r="AE41" s="100"/>
+      <c r="AF41" s="100"/>
+      <c r="AG41" s="100"/>
+      <c r="AH41" s="100"/>
+      <c r="AI41" s="100"/>
     </row>
     <row r="42" spans="1:35" ht="30.75" customHeight="1">
       <c r="A42" s="7">
@@ -53813,18 +54426,18 @@
         <f t="shared" si="5"/>
         <v>-4.22</v>
       </c>
-      <c r="X42" s="140"/>
-      <c r="Y42" s="140"/>
-      <c r="Z42" s="140"/>
-      <c r="AA42" s="140"/>
-      <c r="AB42" s="140"/>
-      <c r="AC42" s="140"/>
-      <c r="AD42" s="140"/>
-      <c r="AE42" s="140"/>
-      <c r="AF42" s="140"/>
-      <c r="AG42" s="140"/>
-      <c r="AH42" s="140"/>
-      <c r="AI42" s="140"/>
+      <c r="X42" s="100"/>
+      <c r="Y42" s="100"/>
+      <c r="Z42" s="100"/>
+      <c r="AA42" s="100"/>
+      <c r="AB42" s="100"/>
+      <c r="AC42" s="100"/>
+      <c r="AD42" s="100"/>
+      <c r="AE42" s="100"/>
+      <c r="AF42" s="100"/>
+      <c r="AG42" s="100"/>
+      <c r="AH42" s="100"/>
+      <c r="AI42" s="100"/>
     </row>
     <row r="43" spans="1:35" ht="30.75" customHeight="1">
       <c r="A43" s="7">
@@ -53901,18 +54514,18 @@
         <f t="shared" si="5"/>
         <v>-4.9800000000000004</v>
       </c>
-      <c r="X43" s="140"/>
-      <c r="Y43" s="140"/>
-      <c r="Z43" s="140"/>
-      <c r="AA43" s="140"/>
-      <c r="AB43" s="140"/>
-      <c r="AC43" s="140"/>
-      <c r="AD43" s="140"/>
-      <c r="AE43" s="140"/>
-      <c r="AF43" s="140"/>
-      <c r="AG43" s="140"/>
-      <c r="AH43" s="140"/>
-      <c r="AI43" s="140"/>
+      <c r="X43" s="100"/>
+      <c r="Y43" s="100"/>
+      <c r="Z43" s="100"/>
+      <c r="AA43" s="100"/>
+      <c r="AB43" s="100"/>
+      <c r="AC43" s="100"/>
+      <c r="AD43" s="100"/>
+      <c r="AE43" s="100"/>
+      <c r="AF43" s="100"/>
+      <c r="AG43" s="100"/>
+      <c r="AH43" s="100"/>
+      <c r="AI43" s="100"/>
     </row>
     <row r="44" spans="1:35" ht="30.75" customHeight="1">
       <c r="A44" s="7">
@@ -53989,18 +54602,18 @@
         <f t="shared" si="5"/>
         <v>-1.85</v>
       </c>
-      <c r="X44" s="140"/>
-      <c r="Y44" s="140"/>
-      <c r="Z44" s="140"/>
-      <c r="AA44" s="140"/>
-      <c r="AB44" s="140"/>
-      <c r="AC44" s="140"/>
-      <c r="AD44" s="140"/>
-      <c r="AE44" s="140"/>
-      <c r="AF44" s="140"/>
-      <c r="AG44" s="140"/>
-      <c r="AH44" s="140"/>
-      <c r="AI44" s="140"/>
+      <c r="X44" s="100"/>
+      <c r="Y44" s="100"/>
+      <c r="Z44" s="100"/>
+      <c r="AA44" s="100"/>
+      <c r="AB44" s="100"/>
+      <c r="AC44" s="100"/>
+      <c r="AD44" s="100"/>
+      <c r="AE44" s="100"/>
+      <c r="AF44" s="100"/>
+      <c r="AG44" s="100"/>
+      <c r="AH44" s="100"/>
+      <c r="AI44" s="100"/>
     </row>
     <row r="45" spans="1:35" ht="30.75" customHeight="1">
       <c r="A45" s="7">
@@ -54077,18 +54690,18 @@
         <f t="shared" si="5"/>
         <v>32.4</v>
       </c>
-      <c r="X45" s="140"/>
-      <c r="Y45" s="140"/>
-      <c r="Z45" s="140"/>
-      <c r="AA45" s="140"/>
-      <c r="AB45" s="140"/>
-      <c r="AC45" s="140"/>
-      <c r="AD45" s="140"/>
-      <c r="AE45" s="140"/>
-      <c r="AF45" s="140"/>
-      <c r="AG45" s="140"/>
-      <c r="AH45" s="140"/>
-      <c r="AI45" s="140"/>
+      <c r="X45" s="100"/>
+      <c r="Y45" s="100"/>
+      <c r="Z45" s="100"/>
+      <c r="AA45" s="100"/>
+      <c r="AB45" s="100"/>
+      <c r="AC45" s="100"/>
+      <c r="AD45" s="100"/>
+      <c r="AE45" s="100"/>
+      <c r="AF45" s="100"/>
+      <c r="AG45" s="100"/>
+      <c r="AH45" s="100"/>
+      <c r="AI45" s="100"/>
     </row>
     <row r="46" spans="1:35" ht="30.75" customHeight="1">
       <c r="A46" s="7">
@@ -54165,18 +54778,18 @@
         <f t="shared" si="5"/>
         <v>10.64</v>
       </c>
-      <c r="X46" s="140"/>
-      <c r="Y46" s="140"/>
-      <c r="Z46" s="140"/>
-      <c r="AA46" s="140"/>
-      <c r="AB46" s="140"/>
-      <c r="AC46" s="140"/>
-      <c r="AD46" s="140"/>
-      <c r="AE46" s="140"/>
-      <c r="AF46" s="140"/>
-      <c r="AG46" s="140"/>
-      <c r="AH46" s="140"/>
-      <c r="AI46" s="140"/>
+      <c r="X46" s="100"/>
+      <c r="Y46" s="100"/>
+      <c r="Z46" s="100"/>
+      <c r="AA46" s="100"/>
+      <c r="AB46" s="100"/>
+      <c r="AC46" s="100"/>
+      <c r="AD46" s="100"/>
+      <c r="AE46" s="100"/>
+      <c r="AF46" s="100"/>
+      <c r="AG46" s="100"/>
+      <c r="AH46" s="100"/>
+      <c r="AI46" s="100"/>
     </row>
     <row r="47" spans="1:35" ht="30.75" customHeight="1">
       <c r="A47" s="7">
@@ -54253,18 +54866,18 @@
         <f t="shared" si="5"/>
         <v>17.13</v>
       </c>
-      <c r="X47" s="140"/>
-      <c r="Y47" s="140"/>
-      <c r="Z47" s="140"/>
-      <c r="AA47" s="140"/>
-      <c r="AB47" s="140"/>
-      <c r="AC47" s="140"/>
-      <c r="AD47" s="140"/>
-      <c r="AE47" s="140"/>
-      <c r="AF47" s="140"/>
-      <c r="AG47" s="140"/>
-      <c r="AH47" s="140"/>
-      <c r="AI47" s="140"/>
+      <c r="X47" s="100"/>
+      <c r="Y47" s="100"/>
+      <c r="Z47" s="100"/>
+      <c r="AA47" s="100"/>
+      <c r="AB47" s="100"/>
+      <c r="AC47" s="100"/>
+      <c r="AD47" s="100"/>
+      <c r="AE47" s="100"/>
+      <c r="AF47" s="100"/>
+      <c r="AG47" s="100"/>
+      <c r="AH47" s="100"/>
+      <c r="AI47" s="100"/>
     </row>
     <row r="48" spans="1:35" ht="30.75" customHeight="1">
       <c r="A48" s="7">
@@ -54341,18 +54954,18 @@
         <f t="shared" si="5"/>
         <v>7.77</v>
       </c>
-      <c r="X48" s="140"/>
-      <c r="Y48" s="140"/>
-      <c r="Z48" s="140"/>
-      <c r="AA48" s="140"/>
-      <c r="AB48" s="140"/>
-      <c r="AC48" s="140"/>
-      <c r="AD48" s="140"/>
-      <c r="AE48" s="140"/>
-      <c r="AF48" s="140"/>
-      <c r="AG48" s="140"/>
-      <c r="AH48" s="140"/>
-      <c r="AI48" s="140"/>
+      <c r="X48" s="100"/>
+      <c r="Y48" s="100"/>
+      <c r="Z48" s="100"/>
+      <c r="AA48" s="100"/>
+      <c r="AB48" s="100"/>
+      <c r="AC48" s="100"/>
+      <c r="AD48" s="100"/>
+      <c r="AE48" s="100"/>
+      <c r="AF48" s="100"/>
+      <c r="AG48" s="100"/>
+      <c r="AH48" s="100"/>
+      <c r="AI48" s="100"/>
     </row>
     <row r="49" spans="1:22" ht="30.75" customHeight="1">
       <c r="A49" s="7">
@@ -54583,11 +55196,11 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="30.75" customHeight="1">
-      <c r="I52" s="94" t="s">
+      <c r="I52" s="135" t="s">
         <v>370</v>
       </c>
-      <c r="J52" s="94"/>
-      <c r="K52" s="94"/>
+      <c r="J52" s="135"/>
+      <c r="K52" s="135"/>
       <c r="L52" s="37"/>
       <c r="M52" s="52"/>
       <c r="N52" s="52"/>
@@ -54625,11 +55238,11 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="30.75" customHeight="1">
-      <c r="I53" s="95" t="s">
+      <c r="I53" s="136" t="s">
         <v>371</v>
       </c>
-      <c r="J53" s="95"/>
-      <c r="K53" s="95"/>
+      <c r="J53" s="136"/>
+      <c r="K53" s="136"/>
       <c r="L53" s="38"/>
       <c r="M53" s="53"/>
       <c r="N53" s="53"/>
@@ -54667,11 +55280,11 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="30.75" customHeight="1">
-      <c r="I54" s="96" t="s">
+      <c r="I54" s="137" t="s">
         <v>372</v>
       </c>
-      <c r="J54" s="96"/>
-      <c r="K54" s="96"/>
+      <c r="J54" s="137"/>
+      <c r="K54" s="137"/>
       <c r="L54" s="39"/>
       <c r="M54" s="54"/>
       <c r="N54" s="54"/>
@@ -54880,6 +55493,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R3:R51">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R2:V2">
     <cfRule type="colorScale" priority="16">
       <colorScale>
@@ -54916,8 +55541,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U3:V51">
-    <cfRule type="colorScale" priority="49">
+  <conditionalFormatting sqref="S3:S51">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T3:T51">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -54940,8 +55577,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:V51">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="U3:V51">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -54952,32 +55589,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T3:T51">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S3:S51">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R51">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="V3:V51">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -55025,35 +55638,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="125" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="86" t="s">
+      <c r="B1" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="127" t="s">
         <v>377</v>
       </c>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="87" t="s">
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="128" t="s">
         <v>525</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88" t="s">
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="129" t="s">
         <v>575</v>
       </c>
-      <c r="J1" s="89"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="92" t="s">
+      <c r="J1" s="130"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="133" t="s">
         <v>210</v>
       </c>
-      <c r="M1" s="93"/>
+      <c r="M1" s="134"/>
     </row>
     <row r="2" spans="1:13" ht="31.5">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
       <c r="C2" s="40" t="s">
         <v>1</v>
       </c>
@@ -55093,7 +55706,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>40</v>
+        <v>693</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>622</v>
@@ -55104,7 +55717,7 @@
       <c r="E3" s="24">
         <v>869.86</v>
       </c>
-      <c r="F3" s="120" t="s">
+      <c r="F3" s="89" t="s">
         <v>622</v>
       </c>
       <c r="G3" s="24">
@@ -55136,7 +55749,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
+        <v>694</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>623</v>
@@ -55166,11 +55779,11 @@
         <v>21.02</v>
       </c>
       <c r="L4" s="48">
-        <f t="shared" ref="L4:L9" si="0">ROUND(IF(E4&lt;H4, -(H4/IF(E4=0,1,E4)), IF(E4=0,1,E4)/IF(H4=0,1,H4)), 2)</f>
+        <f t="shared" ref="L4:L8" si="0">ROUND(IF(E4&lt;H4, -(H4/IF(E4=0,1,E4)), IF(E4=0,1,E4)/IF(H4=0,1,H4)), 2)</f>
         <v>4.93</v>
       </c>
       <c r="M4" s="48">
-        <f t="shared" ref="M4:M9" si="1">ROUND(IF(E4&lt;K4, -(K4/IF(E4=0,1,E4)), IF(E4=0,1,E4)/IF(K4=0,1,K4)), 2)</f>
+        <f t="shared" ref="M4:M8" si="1">ROUND(IF(E4&lt;K4, -(K4/IF(E4=0,1,E4)), IF(E4=0,1,E4)/IF(K4=0,1,K4)), 2)</f>
         <v>20.25</v>
       </c>
     </row>
@@ -55179,7 +55792,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>42</v>
+        <v>695</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>624</v>
@@ -55222,7 +55835,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>43</v>
+        <v>696</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>625</v>
@@ -55265,7 +55878,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>44</v>
+        <v>697</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>626</v>
@@ -55308,7 +55921,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>45</v>
+        <v>698</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>627</v>
@@ -55351,7 +55964,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>506</v>
+        <v>699</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>628</v>
@@ -55393,7 +56006,9 @@
       <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>700</v>
+      </c>
       <c r="C10" s="21" t="s">
         <v>634</v>
       </c>
@@ -55434,7 +56049,9 @@
       <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="C11" s="21" t="s">
         <v>635</v>
       </c>
@@ -55475,7 +56092,9 @@
       <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="8"/>
+      <c r="B12" s="8" t="s">
+        <v>701</v>
+      </c>
       <c r="C12" s="21" t="s">
         <v>636</v>
       </c>
@@ -55516,7 +56135,9 @@
       <c r="A13" s="7">
         <v>11</v>
       </c>
-      <c r="B13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="C13" s="21" t="s">
         <v>637</v>
       </c>
@@ -55557,7 +56178,9 @@
       <c r="A14" s="7">
         <v>12</v>
       </c>
-      <c r="B14" s="8"/>
+      <c r="B14" s="8" t="s">
+        <v>702</v>
+      </c>
       <c r="C14" s="21" t="s">
         <v>638</v>
       </c>
@@ -55598,7 +56221,9 @@
       <c r="A15" s="7">
         <v>13</v>
       </c>
-      <c r="B15" s="8"/>
+      <c r="B15" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="C15" s="21" t="s">
         <v>639</v>
       </c>
@@ -55639,7 +56264,9 @@
       <c r="A16" s="7">
         <v>14</v>
       </c>
-      <c r="B16" s="8"/>
+      <c r="B16" s="8" t="s">
+        <v>703</v>
+      </c>
       <c r="C16" s="21" t="s">
         <v>640</v>
       </c>
@@ -55680,7 +56307,9 @@
       <c r="A17" s="7">
         <v>15</v>
       </c>
-      <c r="B17" s="8"/>
+      <c r="B17" s="8" t="s">
+        <v>704</v>
+      </c>
       <c r="C17" s="21" t="s">
         <v>641</v>
       </c>
@@ -55721,7 +56350,9 @@
       <c r="A18" s="7">
         <v>16</v>
       </c>
-      <c r="B18" s="8"/>
+      <c r="B18" s="8" t="s">
+        <v>705</v>
+      </c>
       <c r="C18" s="21" t="s">
         <v>642</v>
       </c>
@@ -55762,7 +56393,9 @@
       <c r="A19" s="7">
         <v>17</v>
       </c>
-      <c r="B19" s="8"/>
+      <c r="B19" s="8" t="s">
+        <v>706</v>
+      </c>
       <c r="C19" s="21" t="s">
         <v>643</v>
       </c>
@@ -55803,7 +56436,9 @@
       <c r="A20" s="7">
         <v>18</v>
       </c>
-      <c r="B20" s="8"/>
+      <c r="B20" s="8" t="s">
+        <v>707</v>
+      </c>
       <c r="C20" s="21" t="s">
         <v>644</v>
       </c>
@@ -55844,7 +56479,9 @@
       <c r="A21" s="7">
         <v>19</v>
       </c>
-      <c r="B21" s="8"/>
+      <c r="B21" s="8" t="s">
+        <v>708</v>
+      </c>
       <c r="C21" s="21" t="s">
         <v>645</v>
       </c>
@@ -55885,7 +56522,9 @@
       <c r="A22" s="7">
         <v>20</v>
       </c>
-      <c r="B22" s="8"/>
+      <c r="B22" s="8" t="s">
+        <v>709</v>
+      </c>
       <c r="C22" s="21" t="s">
         <v>646</v>
       </c>
@@ -55926,7 +56565,9 @@
       <c r="A23" s="7">
         <v>21</v>
       </c>
-      <c r="B23" s="8"/>
+      <c r="B23" s="8" t="s">
+        <v>710</v>
+      </c>
       <c r="C23" s="21" t="s">
         <v>647</v>
       </c>
@@ -55967,7 +56608,9 @@
       <c r="A24" s="7">
         <v>22</v>
       </c>
-      <c r="B24" s="8"/>
+      <c r="B24" s="8" t="s">
+        <v>711</v>
+      </c>
       <c r="C24" s="21" t="s">
         <v>648</v>
       </c>
@@ -56008,7 +56651,9 @@
       <c r="A25" s="7">
         <v>23</v>
       </c>
-      <c r="B25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="C25" s="21" t="s">
         <v>649</v>
       </c>
@@ -56049,7 +56694,9 @@
       <c r="A26" s="7">
         <v>24</v>
       </c>
-      <c r="B26" s="8"/>
+      <c r="B26" s="8" t="s">
+        <v>712</v>
+      </c>
       <c r="C26" s="21" t="s">
         <v>650</v>
       </c>
@@ -56090,7 +56737,9 @@
       <c r="A27" s="7">
         <v>25</v>
       </c>
-      <c r="B27" s="8"/>
+      <c r="B27" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="C27" s="21" t="s">
         <v>651</v>
       </c>
@@ -56131,7 +56780,9 @@
       <c r="A28" s="7">
         <v>26</v>
       </c>
-      <c r="B28" s="8"/>
+      <c r="B28" s="8" t="s">
+        <v>713</v>
+      </c>
       <c r="C28" s="21" t="s">
         <v>652</v>
       </c>
@@ -56172,7 +56823,9 @@
       <c r="A29" s="7">
         <v>27</v>
       </c>
-      <c r="B29" s="8"/>
+      <c r="B29" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="C29" s="21" t="s">
         <v>653</v>
       </c>
@@ -56213,7 +56866,9 @@
       <c r="A30" s="7">
         <v>28</v>
       </c>
-      <c r="B30" s="8"/>
+      <c r="B30" s="8" t="s">
+        <v>714</v>
+      </c>
       <c r="C30" s="21" t="s">
         <v>654</v>
       </c>
@@ -56254,7 +56909,9 @@
       <c r="A31" s="7">
         <v>29</v>
       </c>
-      <c r="B31" s="8"/>
+      <c r="B31" s="8" t="s">
+        <v>715</v>
+      </c>
       <c r="C31" s="21" t="s">
         <v>655</v>
       </c>
@@ -56295,7 +56952,9 @@
       <c r="A32" s="7">
         <v>30</v>
       </c>
-      <c r="B32" s="8"/>
+      <c r="B32" s="8" t="s">
+        <v>716</v>
+      </c>
       <c r="C32" s="21" t="s">
         <v>656</v>
       </c>
@@ -56336,7 +56995,9 @@
       <c r="A33" s="7">
         <v>31</v>
       </c>
-      <c r="B33" s="8"/>
+      <c r="B33" s="8" t="s">
+        <v>717</v>
+      </c>
       <c r="C33" s="21" t="s">
         <v>657</v>
       </c>
@@ -56377,7 +57038,9 @@
       <c r="A34" s="7">
         <v>32</v>
       </c>
-      <c r="B34" s="8"/>
+      <c r="B34" s="8" t="s">
+        <v>718</v>
+      </c>
       <c r="C34" s="21" t="s">
         <v>658</v>
       </c>
@@ -56418,7 +57081,9 @@
       <c r="A35" s="7">
         <v>33</v>
       </c>
-      <c r="B35" s="8"/>
+      <c r="B35" s="8" t="s">
+        <v>719</v>
+      </c>
       <c r="C35" s="21" t="s">
         <v>659</v>
       </c>
@@ -56459,7 +57124,9 @@
       <c r="A36" s="7">
         <v>34</v>
       </c>
-      <c r="B36" s="8"/>
+      <c r="B36" s="8" t="s">
+        <v>720</v>
+      </c>
       <c r="C36" s="21" t="s">
         <v>660</v>
       </c>
@@ -56500,7 +57167,9 @@
       <c r="A37" s="7">
         <v>35</v>
       </c>
-      <c r="B37" s="8"/>
+      <c r="B37" s="8" t="s">
+        <v>721</v>
+      </c>
       <c r="C37" s="21" t="s">
         <v>661</v>
       </c>
@@ -56541,7 +57210,9 @@
       <c r="A38" s="7">
         <v>36</v>
       </c>
-      <c r="B38" s="8"/>
+      <c r="B38" s="8" t="s">
+        <v>722</v>
+      </c>
       <c r="C38" s="21" t="s">
         <v>662</v>
       </c>
@@ -56582,7 +57253,9 @@
       <c r="A39" s="7">
         <v>37</v>
       </c>
-      <c r="B39" s="8"/>
+      <c r="B39" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="C39" s="21" t="s">
         <v>663</v>
       </c>
@@ -56623,7 +57296,9 @@
       <c r="A40" s="7">
         <v>38</v>
       </c>
-      <c r="B40" s="8"/>
+      <c r="B40" s="8" t="s">
+        <v>723</v>
+      </c>
       <c r="C40" s="21" t="s">
         <v>664</v>
       </c>
@@ -56664,7 +57339,9 @@
       <c r="A41" s="7">
         <v>39</v>
       </c>
-      <c r="B41" s="8"/>
+      <c r="B41" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="C41" s="21" t="s">
         <v>665</v>
       </c>
@@ -56705,7 +57382,9 @@
       <c r="A42" s="7">
         <v>40</v>
       </c>
-      <c r="B42" s="8"/>
+      <c r="B42" s="8" t="s">
+        <v>724</v>
+      </c>
       <c r="C42" s="21" t="s">
         <v>666</v>
       </c>
@@ -56746,7 +57425,9 @@
       <c r="A43" s="7">
         <v>41</v>
       </c>
-      <c r="B43" s="8"/>
+      <c r="B43" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="C43" s="21" t="s">
         <v>667</v>
       </c>
@@ -56787,7 +57468,9 @@
       <c r="A44" s="7">
         <v>42</v>
       </c>
-      <c r="B44" s="8"/>
+      <c r="B44" s="8" t="s">
+        <v>725</v>
+      </c>
       <c r="C44" s="21" t="s">
         <v>668</v>
       </c>
@@ -56828,7 +57511,9 @@
       <c r="A45" s="7">
         <v>43</v>
       </c>
-      <c r="B45" s="8"/>
+      <c r="B45" s="8" t="s">
+        <v>726</v>
+      </c>
       <c r="C45" s="21" t="s">
         <v>669</v>
       </c>
@@ -56869,7 +57554,9 @@
       <c r="A46" s="7">
         <v>44</v>
       </c>
-      <c r="B46" s="8"/>
+      <c r="B46" s="8" t="s">
+        <v>727</v>
+      </c>
       <c r="C46" s="21" t="s">
         <v>670</v>
       </c>
@@ -56910,7 +57597,9 @@
       <c r="A47" s="7">
         <v>45</v>
       </c>
-      <c r="B47" s="8"/>
+      <c r="B47" s="8" t="s">
+        <v>728</v>
+      </c>
       <c r="C47" s="21" t="s">
         <v>671</v>
       </c>
@@ -56951,7 +57640,9 @@
       <c r="A48" s="7">
         <v>46</v>
       </c>
-      <c r="B48" s="8"/>
+      <c r="B48" s="8" t="s">
+        <v>729</v>
+      </c>
       <c r="C48" s="21" t="s">
         <v>672</v>
       </c>
@@ -56992,7 +57683,9 @@
       <c r="A49" s="7">
         <v>47</v>
       </c>
-      <c r="B49" s="8"/>
+      <c r="B49" s="8" t="s">
+        <v>730</v>
+      </c>
       <c r="C49" s="21" t="s">
         <v>673</v>
       </c>
@@ -57033,7 +57726,9 @@
       <c r="A50" s="7">
         <v>48</v>
       </c>
-      <c r="B50" s="8"/>
+      <c r="B50" s="8" t="s">
+        <v>731</v>
+      </c>
       <c r="C50" s="21" t="s">
         <v>674</v>
       </c>
@@ -57074,7 +57769,9 @@
       <c r="A51" s="7">
         <v>49</v>
       </c>
-      <c r="B51" s="8"/>
+      <c r="B51" s="8" t="s">
+        <v>732</v>
+      </c>
       <c r="C51" s="21" t="s">
         <v>675</v>
       </c>
@@ -57112,11 +57809,11 @@
       </c>
     </row>
     <row r="52" spans="1:13" ht="30.75" customHeight="1">
-      <c r="F52" s="94" t="s">
+      <c r="F52" s="135" t="s">
         <v>370</v>
       </c>
-      <c r="G52" s="94"/>
-      <c r="H52" s="94"/>
+      <c r="G52" s="135"/>
+      <c r="H52" s="135"/>
       <c r="I52" s="37"/>
       <c r="J52" s="52"/>
       <c r="K52" s="52"/>
@@ -57130,11 +57827,11 @@
       </c>
     </row>
     <row r="53" spans="1:13" ht="30.75" customHeight="1">
-      <c r="F53" s="95" t="s">
+      <c r="F53" s="136" t="s">
         <v>371</v>
       </c>
-      <c r="G53" s="95"/>
-      <c r="H53" s="95"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
       <c r="I53" s="38"/>
       <c r="J53" s="53"/>
       <c r="K53" s="53"/>
@@ -57148,11 +57845,11 @@
       </c>
     </row>
     <row r="54" spans="1:13" ht="30.75" customHeight="1">
-      <c r="F54" s="96" t="s">
+      <c r="F54" s="137" t="s">
         <v>372</v>
       </c>
-      <c r="G54" s="96"/>
-      <c r="H54" s="96"/>
+      <c r="G54" s="137"/>
+      <c r="H54" s="137"/>
       <c r="I54" s="39"/>
       <c r="J54" s="54"/>
       <c r="K54" s="54"/>
@@ -57185,8 +57882,8 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="M3:M51">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="L3:L51">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -57233,8 +57930,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L51">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="M3:M51">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -57252,6 +57949,702 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527EF143-B1CF-4F4A-B102-B826884793EF}">
+  <dimension ref="A1:R19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" style="119" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.5703125" style="119" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="117" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" style="117" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="18.75">
+      <c r="A1" s="168" t="s">
+        <v>692</v>
+      </c>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
+      <c r="L1" s="165"/>
+      <c r="M1" s="165"/>
+      <c r="N1" s="165"/>
+      <c r="O1" s="165"/>
+      <c r="P1" s="165"/>
+      <c r="Q1" s="165"/>
+    </row>
+    <row r="2" spans="1:18" ht="18.75">
+      <c r="A2" s="168"/>
+      <c r="B2" s="168"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="168"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="113" t="s">
+        <v>757</v>
+      </c>
+      <c r="I2" s="166" t="s">
+        <v>762</v>
+      </c>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
+      <c r="L2" s="166"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="166"/>
+      <c r="P2" s="166"/>
+      <c r="Q2" s="166"/>
+    </row>
+    <row r="3" spans="1:18" ht="18.75">
+      <c r="A3" s="107" t="s">
+        <v>613</v>
+      </c>
+      <c r="B3" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="107" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="114" t="s">
+        <v>690</v>
+      </c>
+      <c r="E3" s="114" t="s">
+        <v>691</v>
+      </c>
+      <c r="G3" s="76"/>
+      <c r="H3" s="113" t="s">
+        <v>758</v>
+      </c>
+      <c r="I3" s="166" t="s">
+        <v>763</v>
+      </c>
+      <c r="J3" s="166"/>
+      <c r="K3" s="166"/>
+      <c r="L3" s="166"/>
+      <c r="M3" s="166"/>
+      <c r="N3" s="166"/>
+      <c r="O3" s="166"/>
+      <c r="P3" s="166"/>
+      <c r="Q3" s="166"/>
+    </row>
+    <row r="4" spans="1:18" ht="45">
+      <c r="A4" s="108" t="s">
+        <v>740</v>
+      </c>
+      <c r="B4" s="108" t="s">
+        <v>733</v>
+      </c>
+      <c r="C4" s="110" t="s">
+        <v>749</v>
+      </c>
+      <c r="D4" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="70">
+        <v>38.06</v>
+      </c>
+      <c r="F4" s="162" t="s">
+        <v>757</v>
+      </c>
+      <c r="G4" s="112"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="165"/>
+      <c r="J4" s="165"/>
+      <c r="K4" s="165"/>
+      <c r="L4" s="165"/>
+      <c r="M4" s="165"/>
+      <c r="N4" s="165"/>
+      <c r="O4" s="165"/>
+      <c r="P4" s="165"/>
+      <c r="Q4" s="165"/>
+    </row>
+    <row r="5" spans="1:18" ht="45">
+      <c r="A5" s="108" t="s">
+        <v>740</v>
+      </c>
+      <c r="B5" s="109" t="s">
+        <v>734</v>
+      </c>
+      <c r="C5" s="110" t="s">
+        <v>750</v>
+      </c>
+      <c r="D5" s="70">
+        <v>0</v>
+      </c>
+      <c r="E5" s="70">
+        <v>21.1</v>
+      </c>
+      <c r="F5" s="163"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="165"/>
+      <c r="K5" s="165"/>
+      <c r="L5" s="165"/>
+      <c r="M5" s="165"/>
+      <c r="N5" s="165"/>
+      <c r="O5" s="165"/>
+      <c r="P5" s="165"/>
+      <c r="Q5" s="165"/>
+    </row>
+    <row r="6" spans="1:18" ht="45">
+      <c r="A6" s="108" t="s">
+        <v>740</v>
+      </c>
+      <c r="B6" s="109" t="s">
+        <v>735</v>
+      </c>
+      <c r="C6" s="110" t="s">
+        <v>751</v>
+      </c>
+      <c r="D6" s="70">
+        <v>0</v>
+      </c>
+      <c r="E6" s="70">
+        <v>18.7</v>
+      </c>
+      <c r="F6" s="163"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="167" t="s">
+        <v>761</v>
+      </c>
+      <c r="I6" s="167"/>
+      <c r="J6" s="167"/>
+      <c r="K6" s="167"/>
+      <c r="L6" s="167"/>
+      <c r="M6" s="167"/>
+      <c r="N6" s="167"/>
+      <c r="O6" s="167"/>
+      <c r="P6" s="167"/>
+      <c r="Q6" s="167"/>
+      <c r="R6" s="167"/>
+    </row>
+    <row r="7" spans="1:18" ht="45">
+      <c r="A7" s="108" t="s">
+        <v>740</v>
+      </c>
+      <c r="B7" s="109" t="s">
+        <v>736</v>
+      </c>
+      <c r="C7" s="110" t="s">
+        <v>752</v>
+      </c>
+      <c r="D7" s="70">
+        <v>0</v>
+      </c>
+      <c r="E7" s="70">
+        <v>8.99</v>
+      </c>
+      <c r="F7" s="163"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="164">
+        <v>20</v>
+      </c>
+      <c r="J7" s="164"/>
+      <c r="K7" s="164">
+        <v>21</v>
+      </c>
+      <c r="L7" s="164"/>
+      <c r="M7" s="164">
+        <v>22</v>
+      </c>
+      <c r="N7" s="164"/>
+      <c r="O7" s="164">
+        <v>23</v>
+      </c>
+      <c r="P7" s="164"/>
+      <c r="Q7" s="164">
+        <v>24</v>
+      </c>
+      <c r="R7" s="164"/>
+    </row>
+    <row r="8" spans="1:18" ht="45">
+      <c r="A8" s="108" t="s">
+        <v>740</v>
+      </c>
+      <c r="B8" s="109" t="s">
+        <v>737</v>
+      </c>
+      <c r="C8" s="110" t="s">
+        <v>753</v>
+      </c>
+      <c r="D8" s="70">
+        <v>0</v>
+      </c>
+      <c r="E8" s="70">
+        <v>0.96</v>
+      </c>
+      <c r="F8" s="163"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="105" t="s">
+        <v>756</v>
+      </c>
+      <c r="I8" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="J8" s="107" t="s">
+        <v>760</v>
+      </c>
+      <c r="K8" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="L8" s="107" t="s">
+        <v>760</v>
+      </c>
+      <c r="M8" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="N8" s="107" t="s">
+        <v>760</v>
+      </c>
+      <c r="O8" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="P8" s="107" t="s">
+        <v>760</v>
+      </c>
+      <c r="Q8" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="R8" s="107" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="45">
+      <c r="A9" s="108" t="s">
+        <v>740</v>
+      </c>
+      <c r="B9" s="109" t="s">
+        <v>738</v>
+      </c>
+      <c r="C9" s="111" t="s">
+        <v>755</v>
+      </c>
+      <c r="D9" s="70">
+        <v>0</v>
+      </c>
+      <c r="E9" s="70">
+        <v>1</v>
+      </c>
+      <c r="F9" s="163"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="105">
+        <v>1</v>
+      </c>
+      <c r="I9" s="97">
+        <v>0.16</v>
+      </c>
+      <c r="J9" s="97">
+        <v>0.15</v>
+      </c>
+      <c r="K9" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="L9" s="97">
+        <v>0.26</v>
+      </c>
+      <c r="M9" s="97">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="N9" s="97">
+        <v>0.61</v>
+      </c>
+      <c r="O9" s="97">
+        <v>1.29</v>
+      </c>
+      <c r="P9" s="97">
+        <v>1.21</v>
+      </c>
+      <c r="Q9" s="124"/>
+      <c r="R9" s="124"/>
+    </row>
+    <row r="10" spans="1:18" ht="45">
+      <c r="A10" s="108" t="s">
+        <v>740</v>
+      </c>
+      <c r="B10" s="109" t="s">
+        <v>739</v>
+      </c>
+      <c r="C10" s="110" t="s">
+        <v>754</v>
+      </c>
+      <c r="D10" s="70">
+        <v>0.01</v>
+      </c>
+      <c r="E10" s="70">
+        <v>1.3</v>
+      </c>
+      <c r="F10" s="163"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="105">
+        <v>2</v>
+      </c>
+      <c r="I10" s="97">
+        <v>2.88</v>
+      </c>
+      <c r="J10" s="97">
+        <v>2.91</v>
+      </c>
+      <c r="K10" s="97">
+        <v>4.78</v>
+      </c>
+      <c r="L10" s="97">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="M10" s="97">
+        <v>8.61</v>
+      </c>
+      <c r="N10" s="97">
+        <v>8.61</v>
+      </c>
+      <c r="O10" s="97">
+        <v>17.78</v>
+      </c>
+      <c r="P10" s="97">
+        <v>17.190000000000001</v>
+      </c>
+      <c r="Q10" s="124"/>
+      <c r="R10" s="124"/>
+    </row>
+    <row r="11" spans="1:18" ht="45">
+      <c r="A11" s="120" t="s">
+        <v>741</v>
+      </c>
+      <c r="B11" s="118" t="s">
+        <v>742</v>
+      </c>
+      <c r="C11" s="115" t="s">
+        <v>764</v>
+      </c>
+      <c r="D11" s="116">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="116">
+        <v>69.87</v>
+      </c>
+      <c r="F11" s="162" t="s">
+        <v>758</v>
+      </c>
+      <c r="H11" s="105">
+        <v>3</v>
+      </c>
+      <c r="I11" s="97">
+        <v>7.3</v>
+      </c>
+      <c r="J11" s="97">
+        <v>8.5</v>
+      </c>
+      <c r="K11" s="97">
+        <v>13.82</v>
+      </c>
+      <c r="L11" s="97">
+        <v>12.05</v>
+      </c>
+      <c r="M11" s="97">
+        <v>27.11</v>
+      </c>
+      <c r="N11" s="97">
+        <v>21.51</v>
+      </c>
+      <c r="O11" s="97">
+        <v>55.68</v>
+      </c>
+      <c r="P11" s="97">
+        <v>46.24</v>
+      </c>
+      <c r="Q11" s="124"/>
+      <c r="R11" s="124"/>
+    </row>
+    <row r="12" spans="1:18" ht="45">
+      <c r="A12" s="120" t="s">
+        <v>741</v>
+      </c>
+      <c r="B12" s="118" t="s">
+        <v>743</v>
+      </c>
+      <c r="C12" s="115" t="s">
+        <v>765</v>
+      </c>
+      <c r="D12" s="116">
+        <v>0</v>
+      </c>
+      <c r="E12" s="116">
+        <v>36.119999999999997</v>
+      </c>
+      <c r="F12" s="163"/>
+      <c r="H12" s="105">
+        <v>4</v>
+      </c>
+      <c r="I12" s="97">
+        <v>0.13</v>
+      </c>
+      <c r="J12" s="97">
+        <v>0.12</v>
+      </c>
+      <c r="K12" s="97">
+        <v>0.21</v>
+      </c>
+      <c r="L12" s="97">
+        <v>0.22</v>
+      </c>
+      <c r="M12" s="97">
+        <v>0.52</v>
+      </c>
+      <c r="N12" s="97">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O12" s="97">
+        <v>0.99</v>
+      </c>
+      <c r="P12" s="97">
+        <v>1.02</v>
+      </c>
+      <c r="Q12" s="124"/>
+      <c r="R12" s="124"/>
+    </row>
+    <row r="13" spans="1:18" ht="45">
+      <c r="A13" s="120" t="s">
+        <v>741</v>
+      </c>
+      <c r="B13" s="118" t="s">
+        <v>744</v>
+      </c>
+      <c r="C13" s="115" t="s">
+        <v>766</v>
+      </c>
+      <c r="D13" s="116">
+        <v>0</v>
+      </c>
+      <c r="E13" s="116">
+        <v>38.89</v>
+      </c>
+      <c r="F13" s="163"/>
+      <c r="H13" s="98">
+        <v>5</v>
+      </c>
+      <c r="I13" s="121">
+        <f>SUM(I9:I12)</f>
+        <v>10.47</v>
+      </c>
+      <c r="J13" s="121">
+        <f>SUM(J9:J12)</f>
+        <v>11.68</v>
+      </c>
+      <c r="K13" s="121">
+        <f t="shared" ref="K13:R13" si="0">SUM(K9:K12)</f>
+        <v>19.07</v>
+      </c>
+      <c r="L13" s="121">
+        <f t="shared" si="0"/>
+        <v>16.759999999999998</v>
+      </c>
+      <c r="M13" s="121">
+        <f t="shared" si="0"/>
+        <v>36.800000000000004</v>
+      </c>
+      <c r="N13" s="121">
+        <f t="shared" si="0"/>
+        <v>31.29</v>
+      </c>
+      <c r="O13" s="121">
+        <f t="shared" si="0"/>
+        <v>75.739999999999995</v>
+      </c>
+      <c r="P13" s="121">
+        <f t="shared" si="0"/>
+        <v>65.66</v>
+      </c>
+      <c r="Q13" s="121">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="121">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="45">
+      <c r="A14" s="120" t="s">
+        <v>741</v>
+      </c>
+      <c r="B14" s="118" t="s">
+        <v>745</v>
+      </c>
+      <c r="C14" s="115" t="s">
+        <v>767</v>
+      </c>
+      <c r="D14" s="116">
+        <v>0</v>
+      </c>
+      <c r="E14" s="116">
+        <v>20.6</v>
+      </c>
+      <c r="F14" s="163"/>
+    </row>
+    <row r="15" spans="1:18" ht="45">
+      <c r="A15" s="120" t="s">
+        <v>741</v>
+      </c>
+      <c r="B15" s="118" t="s">
+        <v>746</v>
+      </c>
+      <c r="C15" s="115" t="s">
+        <v>768</v>
+      </c>
+      <c r="D15" s="116">
+        <v>0</v>
+      </c>
+      <c r="E15" s="116">
+        <v>5.87</v>
+      </c>
+      <c r="F15" s="163"/>
+      <c r="H15" s="123">
+        <v>1</v>
+      </c>
+      <c r="I15" s="161" t="s">
+        <v>678</v>
+      </c>
+      <c r="J15" s="161"/>
+      <c r="K15" s="161"/>
+      <c r="L15" s="161"/>
+      <c r="M15" s="161"/>
+      <c r="N15" s="161"/>
+      <c r="O15" s="161"/>
+      <c r="P15" s="161"/>
+      <c r="Q15" s="161"/>
+    </row>
+    <row r="16" spans="1:18" ht="45">
+      <c r="A16" s="120" t="s">
+        <v>741</v>
+      </c>
+      <c r="B16" s="118" t="s">
+        <v>747</v>
+      </c>
+      <c r="C16" s="115" t="s">
+        <v>769</v>
+      </c>
+      <c r="D16" s="116">
+        <v>0</v>
+      </c>
+      <c r="E16" s="116">
+        <v>6.09</v>
+      </c>
+      <c r="F16" s="163"/>
+      <c r="H16" s="123">
+        <v>2</v>
+      </c>
+      <c r="I16" s="161" t="s">
+        <v>677</v>
+      </c>
+      <c r="J16" s="161"/>
+      <c r="K16" s="161"/>
+      <c r="L16" s="161"/>
+      <c r="M16" s="161"/>
+      <c r="N16" s="161"/>
+      <c r="O16" s="161"/>
+      <c r="P16" s="161"/>
+      <c r="Q16" s="161"/>
+    </row>
+    <row r="17" spans="1:17" ht="45">
+      <c r="A17" s="120" t="s">
+        <v>741</v>
+      </c>
+      <c r="B17" s="118" t="s">
+        <v>748</v>
+      </c>
+      <c r="C17" s="115" t="s">
+        <v>770</v>
+      </c>
+      <c r="D17" s="116">
+        <v>0</v>
+      </c>
+      <c r="E17" s="116">
+        <v>6.42</v>
+      </c>
+      <c r="F17" s="163"/>
+      <c r="H17" s="123">
+        <v>3</v>
+      </c>
+      <c r="I17" s="161" t="s">
+        <v>679</v>
+      </c>
+      <c r="J17" s="161"/>
+      <c r="K17" s="161"/>
+      <c r="L17" s="161"/>
+      <c r="M17" s="161"/>
+      <c r="N17" s="161"/>
+      <c r="O17" s="161"/>
+      <c r="P17" s="161"/>
+      <c r="Q17" s="161"/>
+    </row>
+    <row r="18" spans="1:17" ht="18.75">
+      <c r="H18" s="123">
+        <v>4</v>
+      </c>
+      <c r="I18" s="161" t="s">
+        <v>680</v>
+      </c>
+      <c r="J18" s="161"/>
+      <c r="K18" s="161"/>
+      <c r="L18" s="161"/>
+      <c r="M18" s="161"/>
+      <c r="N18" s="161"/>
+      <c r="O18" s="161"/>
+      <c r="P18" s="161"/>
+      <c r="Q18" s="161"/>
+    </row>
+    <row r="19" spans="1:17" ht="18.75">
+      <c r="H19" s="123">
+        <v>5</v>
+      </c>
+      <c r="I19" s="161" t="s">
+        <v>681</v>
+      </c>
+      <c r="J19" s="161"/>
+      <c r="K19" s="161"/>
+      <c r="L19" s="161"/>
+      <c r="M19" s="161"/>
+      <c r="N19" s="161"/>
+      <c r="O19" s="161"/>
+      <c r="P19" s="161"/>
+      <c r="Q19" s="161"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="H6:R6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="I1:Q1"/>
+    <mergeCell ref="I2:Q2"/>
+    <mergeCell ref="I3:Q3"/>
+    <mergeCell ref="I4:Q4"/>
+    <mergeCell ref="I5:Q5"/>
+    <mergeCell ref="F4:F10"/>
+    <mergeCell ref="F11:F17"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="I15:Q15"/>
+    <mergeCell ref="I16:Q16"/>
+    <mergeCell ref="I17:Q17"/>
+    <mergeCell ref="I18:Q18"/>
+    <mergeCell ref="I19:Q19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33506B9C-A37F-4F57-977C-155239694EF5}">
   <dimension ref="A1:AH59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -57268,62 +58661,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="21.75" thickBot="1">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="172" t="s">
         <v>682</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="L1" s="107" t="s">
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
+      <c r="J1" s="172"/>
+      <c r="L1" s="169" t="s">
         <v>629</v>
       </c>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="109"/>
-      <c r="X1" s="107" t="s">
+      <c r="M1" s="170"/>
+      <c r="N1" s="170"/>
+      <c r="O1" s="170"/>
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="170"/>
+      <c r="S1" s="170"/>
+      <c r="T1" s="170"/>
+      <c r="U1" s="170"/>
+      <c r="V1" s="171"/>
+      <c r="X1" s="169" t="s">
         <v>631</v>
       </c>
-      <c r="Y1" s="108"/>
-      <c r="Z1" s="108"/>
-      <c r="AA1" s="108"/>
-      <c r="AB1" s="108"/>
-      <c r="AC1" s="108"/>
-      <c r="AD1" s="108"/>
-      <c r="AE1" s="108"/>
-      <c r="AF1" s="108"/>
-      <c r="AG1" s="108"/>
-      <c r="AH1" s="109"/>
+      <c r="Y1" s="170"/>
+      <c r="Z1" s="170"/>
+      <c r="AA1" s="170"/>
+      <c r="AB1" s="170"/>
+      <c r="AC1" s="170"/>
+      <c r="AD1" s="170"/>
+      <c r="AE1" s="170"/>
+      <c r="AF1" s="170"/>
+      <c r="AG1" s="170"/>
+      <c r="AH1" s="171"/>
     </row>
     <row r="2" spans="1:34" ht="36.75" customHeight="1">
       <c r="A2" s="61"/>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="127" t="s">
         <v>614</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="s">
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="128" t="s">
         <v>617</v>
       </c>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="111" t="s">
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="173" t="s">
         <v>618</v>
       </c>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
       <c r="L2" s="75"/>
       <c r="M2" s="76"/>
       <c r="N2" s="76"/>
@@ -57693,12 +59086,12 @@
       <c r="A9" s="63">
         <v>21</v>
       </c>
-      <c r="B9" s="113"/>
-      <c r="C9" s="113"/>
-      <c r="D9" s="113"/>
-      <c r="E9" s="113"/>
-      <c r="F9" s="113"/>
-      <c r="G9" s="113"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
       <c r="H9" s="67"/>
       <c r="I9" s="67"/>
       <c r="J9" s="67"/>
@@ -57813,18 +59206,18 @@
       <c r="AH11" s="77"/>
     </row>
     <row r="12" spans="1:34" ht="21">
-      <c r="A12" s="110" t="s">
+      <c r="A12" s="172" t="s">
         <v>621</v>
       </c>
-      <c r="B12" s="110"/>
-      <c r="C12" s="110"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
+      <c r="B12" s="172"/>
+      <c r="C12" s="172"/>
+      <c r="D12" s="172"/>
+      <c r="E12" s="172"/>
+      <c r="F12" s="172"/>
+      <c r="G12" s="172"/>
+      <c r="H12" s="172"/>
+      <c r="I12" s="172"/>
+      <c r="J12" s="172"/>
       <c r="L12" s="75"/>
       <c r="M12" s="76"/>
       <c r="N12" s="76"/>
@@ -57850,21 +59243,21 @@
     </row>
     <row r="13" spans="1:34" ht="35.25" customHeight="1">
       <c r="A13" s="61"/>
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="127" t="s">
         <v>614</v>
       </c>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="87" t="s">
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="128" t="s">
         <v>617</v>
       </c>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="111" t="s">
+      <c r="F13" s="128"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="173" t="s">
         <v>618</v>
       </c>
-      <c r="I13" s="111"/>
-      <c r="J13" s="111"/>
+      <c r="I13" s="173"/>
+      <c r="J13" s="173"/>
       <c r="L13" s="75"/>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
@@ -58133,19 +59526,19 @@
         <f>'15 Elementos'!T54</f>
         <v>1.1399999999999999</v>
       </c>
-      <c r="L18" s="107" t="s">
+      <c r="L18" s="169" t="s">
         <v>630</v>
       </c>
-      <c r="M18" s="108"/>
-      <c r="N18" s="108"/>
-      <c r="O18" s="108"/>
-      <c r="P18" s="108"/>
-      <c r="Q18" s="108"/>
-      <c r="R18" s="108"/>
-      <c r="S18" s="108"/>
-      <c r="T18" s="108"/>
-      <c r="U18" s="108"/>
-      <c r="V18" s="109"/>
+      <c r="M18" s="170"/>
+      <c r="N18" s="170"/>
+      <c r="O18" s="170"/>
+      <c r="P18" s="170"/>
+      <c r="Q18" s="170"/>
+      <c r="R18" s="170"/>
+      <c r="S18" s="170"/>
+      <c r="T18" s="170"/>
+      <c r="U18" s="170"/>
+      <c r="V18" s="171"/>
       <c r="X18" s="75"/>
       <c r="Y18" s="76"/>
       <c r="Z18" s="76"/>
@@ -58420,18 +59813,18 @@
       <c r="AH24" s="77"/>
     </row>
     <row r="25" spans="1:34">
-      <c r="A25" s="133" t="s">
+      <c r="A25" s="180" t="s">
         <v>683</v>
       </c>
-      <c r="B25" s="133"/>
-      <c r="C25" s="133"/>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="133"/>
-      <c r="I25" s="133"/>
-      <c r="J25" s="133"/>
+      <c r="B25" s="180"/>
+      <c r="C25" s="180"/>
+      <c r="D25" s="180"/>
+      <c r="E25" s="180"/>
+      <c r="F25" s="180"/>
+      <c r="G25" s="180"/>
+      <c r="H25" s="180"/>
+      <c r="I25" s="180"/>
+      <c r="J25" s="180"/>
       <c r="L25" s="75"/>
       <c r="M25" s="76"/>
       <c r="N25" s="76"/>
@@ -58456,16 +59849,16 @@
       <c r="AH25" s="77"/>
     </row>
     <row r="26" spans="1:34">
-      <c r="A26" s="134"/>
-      <c r="B26" s="134"/>
-      <c r="C26" s="134"/>
-      <c r="D26" s="134"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="134"/>
-      <c r="I26" s="134"/>
-      <c r="J26" s="134"/>
+      <c r="A26" s="181"/>
+      <c r="B26" s="181"/>
+      <c r="C26" s="181"/>
+      <c r="D26" s="181"/>
+      <c r="E26" s="181"/>
+      <c r="F26" s="181"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="181"/>
+      <c r="I26" s="181"/>
+      <c r="J26" s="181"/>
       <c r="L26" s="75"/>
       <c r="M26" s="76"/>
       <c r="N26" s="76"/>
@@ -58490,26 +59883,26 @@
       <c r="AH26" s="77"/>
     </row>
     <row r="27" spans="1:34" ht="30">
-      <c r="A27" s="130" t="s">
+      <c r="A27" s="94" t="s">
         <v>676</v>
       </c>
-      <c r="B27" s="126" t="s">
+      <c r="B27" s="157" t="s">
         <v>686</v>
       </c>
-      <c r="C27" s="126"/>
-      <c r="D27" s="127" t="s">
+      <c r="C27" s="157"/>
+      <c r="D27" s="174" t="s">
         <v>685</v>
       </c>
-      <c r="E27" s="128"/>
-      <c r="F27" s="129" t="s">
+      <c r="E27" s="175"/>
+      <c r="F27" s="159" t="s">
         <v>684</v>
       </c>
-      <c r="G27" s="129"/>
-      <c r="H27" s="129"/>
-      <c r="I27" s="131" t="s">
+      <c r="G27" s="159"/>
+      <c r="H27" s="159"/>
+      <c r="I27" s="95" t="s">
         <v>529</v>
       </c>
-      <c r="J27" s="132" t="s">
+      <c r="J27" s="96" t="s">
         <v>579</v>
       </c>
       <c r="L27" s="75"/>
@@ -58536,27 +59929,27 @@
       <c r="AH27" s="77"/>
     </row>
     <row r="28" spans="1:34" ht="18.75">
-      <c r="A28" s="121">
+      <c r="A28" s="90">
         <v>1</v>
       </c>
-      <c r="B28" s="135">
+      <c r="B28" s="161">
         <v>0.35</v>
       </c>
-      <c r="C28" s="135"/>
-      <c r="D28" s="136">
+      <c r="C28" s="161"/>
+      <c r="D28" s="176">
         <v>0.33</v>
       </c>
-      <c r="E28" s="137"/>
-      <c r="F28" s="135">
+      <c r="E28" s="177"/>
+      <c r="F28" s="161">
         <v>0.27</v>
       </c>
-      <c r="G28" s="135"/>
-      <c r="H28" s="135"/>
-      <c r="I28" s="139">
+      <c r="G28" s="161"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="99">
         <f>B28/D28</f>
         <v>1.0606060606060606</v>
       </c>
-      <c r="J28" s="139">
+      <c r="J28" s="99">
         <f>B28/F28</f>
         <v>1.2962962962962961</v>
       </c>
@@ -58584,28 +59977,28 @@
       <c r="AH28" s="77"/>
     </row>
     <row r="29" spans="1:34" ht="18.75">
-      <c r="A29" s="121">
+      <c r="A29" s="90">
         <v>2</v>
       </c>
-      <c r="B29" s="135">
+      <c r="B29" s="161">
         <v>829.35</v>
       </c>
-      <c r="C29" s="135"/>
-      <c r="D29" s="136">
+      <c r="C29" s="161"/>
+      <c r="D29" s="176">
         <v>148.22</v>
       </c>
-      <c r="E29" s="137"/>
-      <c r="F29" s="135">
+      <c r="E29" s="177"/>
+      <c r="F29" s="161">
         <v>4.28</v>
       </c>
-      <c r="G29" s="135"/>
-      <c r="H29" s="135"/>
-      <c r="I29" s="139">
-        <f t="shared" ref="I29:I32" si="2">B29/D29</f>
+      <c r="G29" s="161"/>
+      <c r="H29" s="161"/>
+      <c r="I29" s="99">
+        <f t="shared" ref="I29:I31" si="2">B29/D29</f>
         <v>5.595398731615167</v>
       </c>
-      <c r="J29" s="139">
-        <f t="shared" ref="J29:J32" si="3">B29/F29</f>
+      <c r="J29" s="99">
+        <f t="shared" ref="J29:J31" si="3">B29/F29</f>
         <v>193.77336448598129</v>
       </c>
       <c r="L29" s="75"/>
@@ -58632,27 +60025,27 @@
       <c r="AH29" s="77"/>
     </row>
     <row r="30" spans="1:34" ht="18.75">
-      <c r="A30" s="121">
+      <c r="A30" s="90">
         <v>3</v>
       </c>
-      <c r="B30" s="135">
+      <c r="B30" s="161">
         <v>14.05</v>
       </c>
-      <c r="C30" s="135"/>
-      <c r="D30" s="136">
+      <c r="C30" s="161"/>
+      <c r="D30" s="176">
         <v>20.03</v>
       </c>
-      <c r="E30" s="137"/>
-      <c r="F30" s="135">
+      <c r="E30" s="177"/>
+      <c r="F30" s="161">
         <v>13.32</v>
       </c>
-      <c r="G30" s="135"/>
-      <c r="H30" s="135"/>
-      <c r="I30" s="139">
+      <c r="G30" s="161"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="99">
         <f t="shared" si="2"/>
         <v>0.70144782825761354</v>
       </c>
-      <c r="J30" s="139">
+      <c r="J30" s="99">
         <f t="shared" si="3"/>
         <v>1.0548048048048049</v>
       </c>
@@ -58680,27 +60073,27 @@
       <c r="AH30" s="77"/>
     </row>
     <row r="31" spans="1:34" ht="18.75">
-      <c r="A31" s="121">
+      <c r="A31" s="90">
         <v>4</v>
       </c>
-      <c r="B31" s="135">
+      <c r="B31" s="161">
         <v>0.23</v>
       </c>
-      <c r="C31" s="135"/>
-      <c r="D31" s="135">
+      <c r="C31" s="161"/>
+      <c r="D31" s="161">
         <v>22.95</v>
       </c>
-      <c r="E31" s="135"/>
-      <c r="F31" s="135">
+      <c r="E31" s="161"/>
+      <c r="F31" s="161">
         <v>23.72</v>
       </c>
-      <c r="G31" s="135"/>
-      <c r="H31" s="135"/>
-      <c r="I31" s="139">
+      <c r="G31" s="161"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="99">
         <f t="shared" si="2"/>
         <v>1.0021786492374729E-2</v>
       </c>
-      <c r="J31" s="139">
+      <c r="J31" s="99">
         <f t="shared" si="3"/>
         <v>9.6964586846543018E-3</v>
       </c>
@@ -58728,25 +60121,25 @@
       <c r="AH31" s="77"/>
     </row>
     <row r="32" spans="1:34" ht="18.75">
-      <c r="A32" s="125">
+      <c r="A32" s="93">
         <v>5</v>
       </c>
-      <c r="B32" s="138">
+      <c r="B32" s="179">
         <f>SUM(B28:C31)</f>
         <v>843.98</v>
       </c>
-      <c r="C32" s="138"/>
-      <c r="D32" s="138">
+      <c r="C32" s="179"/>
+      <c r="D32" s="179">
         <f>SUM(D28:E31)</f>
         <v>191.53</v>
       </c>
-      <c r="E32" s="138"/>
-      <c r="F32" s="138">
+      <c r="E32" s="179"/>
+      <c r="F32" s="179">
         <f>SUM(F28:H31)</f>
         <v>41.59</v>
       </c>
-      <c r="G32" s="138"/>
-      <c r="H32" s="138"/>
+      <c r="G32" s="179"/>
+      <c r="H32" s="179"/>
       <c r="I32" s="73">
         <f>B32/D32</f>
         <v>4.4065159505038372</v>
@@ -58803,20 +60196,20 @@
       <c r="AH33" s="77"/>
     </row>
     <row r="34" spans="1:34" ht="19.5" thickBot="1">
-      <c r="A34" s="123">
+      <c r="A34" s="92">
         <v>1</v>
       </c>
-      <c r="B34" s="124" t="s">
+      <c r="B34" s="178" t="s">
         <v>678</v>
       </c>
-      <c r="C34" s="124"/>
-      <c r="D34" s="124"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="124"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="124"/>
-      <c r="I34" s="124"/>
-      <c r="J34" s="124"/>
+      <c r="C34" s="178"/>
+      <c r="D34" s="178"/>
+      <c r="E34" s="178"/>
+      <c r="F34" s="178"/>
+      <c r="G34" s="178"/>
+      <c r="H34" s="178"/>
+      <c r="I34" s="178"/>
+      <c r="J34" s="178"/>
       <c r="L34" s="75"/>
       <c r="M34" s="76"/>
       <c r="N34" s="76"/>
@@ -58841,20 +60234,20 @@
       <c r="AH34" s="80"/>
     </row>
     <row r="35" spans="1:34" ht="18.75">
-      <c r="A35" s="123">
+      <c r="A35" s="92">
         <v>2</v>
       </c>
-      <c r="B35" s="124" t="s">
+      <c r="B35" s="178" t="s">
         <v>677</v>
       </c>
-      <c r="C35" s="124"/>
-      <c r="D35" s="124"/>
-      <c r="E35" s="124"/>
-      <c r="F35" s="124"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="124"/>
-      <c r="I35" s="124"/>
-      <c r="J35" s="124"/>
+      <c r="C35" s="178"/>
+      <c r="D35" s="178"/>
+      <c r="E35" s="178"/>
+      <c r="F35" s="178"/>
+      <c r="G35" s="178"/>
+      <c r="H35" s="178"/>
+      <c r="I35" s="178"/>
+      <c r="J35" s="178"/>
       <c r="L35" s="75"/>
       <c r="M35" s="76"/>
       <c r="N35" s="76"/>
@@ -58868,20 +60261,20 @@
       <c r="V35" s="77"/>
     </row>
     <row r="36" spans="1:34" ht="18.75">
-      <c r="A36" s="123">
+      <c r="A36" s="92">
         <v>3</v>
       </c>
-      <c r="B36" s="124" t="s">
+      <c r="B36" s="178" t="s">
         <v>679</v>
       </c>
-      <c r="C36" s="124"/>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="124"/>
+      <c r="C36" s="178"/>
+      <c r="D36" s="178"/>
+      <c r="E36" s="178"/>
+      <c r="F36" s="178"/>
+      <c r="G36" s="178"/>
+      <c r="H36" s="178"/>
+      <c r="I36" s="178"/>
+      <c r="J36" s="178"/>
       <c r="L36" s="75"/>
       <c r="M36" s="76"/>
       <c r="N36" s="76"/>
@@ -58895,20 +60288,20 @@
       <c r="V36" s="77"/>
     </row>
     <row r="37" spans="1:34" ht="18.75">
-      <c r="A37" s="123">
+      <c r="A37" s="92">
         <v>4</v>
       </c>
-      <c r="B37" s="124" t="s">
+      <c r="B37" s="178" t="s">
         <v>680</v>
       </c>
-      <c r="C37" s="124"/>
-      <c r="D37" s="124"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="124"/>
-      <c r="G37" s="124"/>
-      <c r="H37" s="124"/>
-      <c r="I37" s="124"/>
-      <c r="J37" s="124"/>
+      <c r="C37" s="178"/>
+      <c r="D37" s="178"/>
+      <c r="E37" s="178"/>
+      <c r="F37" s="178"/>
+      <c r="G37" s="178"/>
+      <c r="H37" s="178"/>
+      <c r="I37" s="178"/>
+      <c r="J37" s="178"/>
       <c r="L37" s="75"/>
       <c r="M37" s="76"/>
       <c r="N37" s="76"/>
@@ -58922,20 +60315,20 @@
       <c r="V37" s="77"/>
     </row>
     <row r="38" spans="1:34" ht="18.75">
-      <c r="A38" s="123">
+      <c r="A38" s="92">
         <v>5</v>
       </c>
-      <c r="B38" s="124" t="s">
+      <c r="B38" s="178" t="s">
         <v>681</v>
       </c>
-      <c r="C38" s="124"/>
-      <c r="D38" s="124"/>
-      <c r="E38" s="124"/>
-      <c r="F38" s="124"/>
-      <c r="G38" s="124"/>
-      <c r="H38" s="124"/>
-      <c r="I38" s="124"/>
-      <c r="J38" s="124"/>
+      <c r="C38" s="178"/>
+      <c r="D38" s="178"/>
+      <c r="E38" s="178"/>
+      <c r="F38" s="178"/>
+      <c r="G38" s="178"/>
+      <c r="H38" s="178"/>
+      <c r="I38" s="178"/>
+      <c r="J38" s="178"/>
       <c r="L38" s="75"/>
       <c r="M38" s="76"/>
       <c r="N38" s="76"/>
@@ -58949,7 +60342,7 @@
       <c r="V38" s="77"/>
     </row>
     <row r="39" spans="1:34" ht="18.75">
-      <c r="A39" s="122"/>
+      <c r="A39" s="91"/>
       <c r="H39" s="76"/>
       <c r="L39" s="75"/>
       <c r="M39" s="76"/>
@@ -59247,22 +60640,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A25:J26"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
     <mergeCell ref="B38:J38"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B37:J37"/>
     <mergeCell ref="X1:AH1"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
@@ -59278,250 +60674,10 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A25:J26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3442CB58-E47F-4D67-9128-0E093C9B1AEB}">
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="27" customHeight="1">
-      <c r="A1" s="112" t="s">
-        <v>164</v>
-      </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75">
-      <c r="A2" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75">
-      <c r="A3" s="3"/>
-      <c r="B3" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75">
-      <c r="A8" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Proyecto Final ADA-PCD Pruebas.xlsx
+++ b/Proyecto Final ADA-PCD Pruebas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University\ada\Proyecto-ADA-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFCEAB5-B9E2-4AB6-923A-652802969269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15A67CC-5706-4E60-897B-185D11F1E52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14880" yWindow="840" windowWidth="21375" windowHeight="19425" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15225" yWindow="1185" windowWidth="21375" windowHeight="19425" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plantilla" sheetId="14" r:id="rId1"/>
@@ -3880,18 +3880,6 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3918,6 +3906,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3947,12 +3947,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3988,7 +3982,25 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3997,19 +4009,19 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4031,18 +4043,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -36356,44 +36356,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="126" t="s">
+      <c r="B1" s="134" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="135" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="127" t="s">
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="136" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="128" t="s">
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="137" t="s">
         <v>525</v>
       </c>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="129" t="s">
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="125" t="s">
         <v>575</v>
       </c>
-      <c r="M1" s="130"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="132" t="s">
+      <c r="M1" s="126"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="128" t="s">
         <v>210</v>
       </c>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="134"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="130"/>
     </row>
     <row r="2" spans="1:20" ht="31.5">
-      <c r="A2" s="125"/>
-      <c r="B2" s="125"/>
+      <c r="A2" s="134"/>
+      <c r="B2" s="134"/>
       <c r="C2" s="13" t="s">
         <v>1</v>
       </c>
@@ -38550,11 +38550,11 @@
       </c>
     </row>
     <row r="53" spans="1:20" ht="18.75">
-      <c r="I53" s="135" t="s">
+      <c r="I53" s="131" t="s">
         <v>370</v>
       </c>
-      <c r="J53" s="135"/>
-      <c r="K53" s="135"/>
+      <c r="J53" s="131"/>
+      <c r="K53" s="131"/>
       <c r="L53" s="26"/>
       <c r="M53" s="45"/>
       <c r="N53" s="45"/>
@@ -38584,11 +38584,11 @@
       </c>
     </row>
     <row r="54" spans="1:20" ht="18.75">
-      <c r="I54" s="136" t="s">
+      <c r="I54" s="132" t="s">
         <v>371</v>
       </c>
-      <c r="J54" s="136"/>
-      <c r="K54" s="136"/>
+      <c r="J54" s="132"/>
+      <c r="K54" s="132"/>
       <c r="L54" s="27"/>
       <c r="M54" s="46"/>
       <c r="N54" s="46"/>
@@ -38618,11 +38618,11 @@
       </c>
     </row>
     <row r="55" spans="1:20" ht="18.75">
-      <c r="I55" s="137" t="s">
+      <c r="I55" s="133" t="s">
         <v>372</v>
       </c>
-      <c r="J55" s="137"/>
-      <c r="K55" s="137"/>
+      <c r="J55" s="133"/>
+      <c r="K55" s="133"/>
       <c r="L55" s="28"/>
       <c r="M55" s="47"/>
       <c r="N55" s="47"/>
@@ -38673,16 +38673,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:T1"/>
     <mergeCell ref="I53:K53"/>
     <mergeCell ref="I54:K54"/>
     <mergeCell ref="I55:K55"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="O1:O52 O56:O1048576">
     <cfRule type="colorScale" priority="3">
@@ -38984,37 +38984,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="126" t="s">
+      <c r="B1" s="134" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="135" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="127" t="s">
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="136" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="128" t="s">
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="137" t="s">
         <v>525</v>
       </c>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="132" t="s">
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="128" t="s">
         <v>210</v>
       </c>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
     </row>
     <row r="2" spans="1:15" ht="31.5">
-      <c r="A2" s="125"/>
-      <c r="B2" s="125"/>
+      <c r="A2" s="134"/>
+      <c r="B2" s="134"/>
       <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
@@ -41555,11 +41555,11 @@
       </c>
     </row>
     <row r="52" spans="1:15" ht="18.75">
-      <c r="I52" s="135" t="s">
+      <c r="I52" s="131" t="s">
         <v>370</v>
       </c>
-      <c r="J52" s="135"/>
-      <c r="K52" s="135"/>
+      <c r="J52" s="131"/>
+      <c r="K52" s="131"/>
       <c r="L52" s="18">
         <f>AVERAGE(L$3:L$51)</f>
         <v>7.6530612244897961E-2</v>
@@ -41578,11 +41578,11 @@
       </c>
     </row>
     <row r="53" spans="1:15" ht="18.75">
-      <c r="I53" s="136" t="s">
+      <c r="I53" s="132" t="s">
         <v>371</v>
       </c>
-      <c r="J53" s="136"/>
-      <c r="K53" s="136"/>
+      <c r="J53" s="132"/>
+      <c r="K53" s="132"/>
       <c r="L53" s="14">
         <f>MIN(L$3:L$51)</f>
         <v>0</v>
@@ -41601,11 +41601,11 @@
       </c>
     </row>
     <row r="54" spans="1:15" ht="18.75">
-      <c r="I54" s="137" t="s">
+      <c r="I54" s="133" t="s">
         <v>372</v>
       </c>
-      <c r="J54" s="137"/>
-      <c r="K54" s="137"/>
+      <c r="J54" s="133"/>
+      <c r="K54" s="133"/>
       <c r="L54" s="16">
         <f>MAX(L$3:L$51)</f>
         <v>0.25</v>
@@ -41809,37 +41809,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="126" t="s">
+      <c r="B1" s="134" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="135" t="s">
         <v>177</v>
       </c>
       <c r="D1" s="142"/>
       <c r="E1" s="142"/>
-      <c r="F1" s="127" t="s">
+      <c r="F1" s="136" t="s">
         <v>377</v>
       </c>
       <c r="G1" s="143"/>
       <c r="H1" s="143"/>
-      <c r="I1" s="128" t="s">
+      <c r="I1" s="137" t="s">
         <v>525</v>
       </c>
       <c r="J1" s="144"/>
       <c r="K1" s="144"/>
-      <c r="L1" s="132" t="s">
+      <c r="L1" s="128" t="s">
         <v>210</v>
       </c>
-      <c r="M1" s="133"/>
+      <c r="M1" s="129"/>
       <c r="N1" s="138"/>
       <c r="O1" s="138"/>
     </row>
     <row r="2" spans="1:15" ht="31.5">
-      <c r="A2" s="125"/>
-      <c r="B2" s="125"/>
+      <c r="A2" s="134"/>
+      <c r="B2" s="134"/>
       <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
@@ -44381,7 +44381,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" ht="18.75">
-      <c r="I52" s="135" t="s">
+      <c r="I52" s="131" t="s">
         <v>370</v>
       </c>
       <c r="J52" s="139"/>
@@ -44404,7 +44404,7 @@
       </c>
     </row>
     <row r="53" spans="1:15" ht="18.75">
-      <c r="I53" s="136" t="s">
+      <c r="I53" s="132" t="s">
         <v>371</v>
       </c>
       <c r="J53" s="140"/>
@@ -44427,7 +44427,7 @@
       </c>
     </row>
     <row r="54" spans="1:15" ht="18.75">
-      <c r="I54" s="137" t="s">
+      <c r="I54" s="133" t="s">
         <v>372</v>
       </c>
       <c r="J54" s="141"/>
@@ -44636,37 +44636,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="126" t="s">
+      <c r="B1" s="134" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="135" t="s">
         <v>177</v>
       </c>
       <c r="D1" s="142"/>
       <c r="E1" s="142"/>
-      <c r="F1" s="127" t="s">
+      <c r="F1" s="136" t="s">
         <v>377</v>
       </c>
       <c r="G1" s="143"/>
       <c r="H1" s="143"/>
-      <c r="I1" s="128" t="s">
+      <c r="I1" s="137" t="s">
         <v>525</v>
       </c>
       <c r="J1" s="144"/>
       <c r="K1" s="144"/>
-      <c r="L1" s="132" t="s">
+      <c r="L1" s="128" t="s">
         <v>210</v>
       </c>
-      <c r="M1" s="133"/>
+      <c r="M1" s="129"/>
       <c r="N1" s="138"/>
       <c r="O1" s="138"/>
     </row>
     <row r="2" spans="1:15" ht="31.5">
-      <c r="A2" s="125"/>
-      <c r="B2" s="125"/>
+      <c r="A2" s="134"/>
+      <c r="B2" s="134"/>
       <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
@@ -47208,7 +47208,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" ht="18.75">
-      <c r="I52" s="135" t="s">
+      <c r="I52" s="131" t="s">
         <v>370</v>
       </c>
       <c r="J52" s="139"/>
@@ -47231,7 +47231,7 @@
       </c>
     </row>
     <row r="53" spans="1:15" ht="18.75">
-      <c r="I53" s="136" t="s">
+      <c r="I53" s="132" t="s">
         <v>371</v>
       </c>
       <c r="J53" s="140"/>
@@ -47254,7 +47254,7 @@
       </c>
     </row>
     <row r="54" spans="1:15" ht="18.75">
-      <c r="I54" s="137" t="s">
+      <c r="I54" s="133" t="s">
         <v>372</v>
       </c>
       <c r="J54" s="141"/>
@@ -47466,44 +47466,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="126" t="s">
+      <c r="B1" s="134" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="135" t="s">
         <v>177</v>
       </c>
       <c r="D1" s="142"/>
       <c r="E1" s="142"/>
-      <c r="F1" s="127" t="s">
+      <c r="F1" s="136" t="s">
         <v>377</v>
       </c>
       <c r="G1" s="143"/>
       <c r="H1" s="143"/>
-      <c r="I1" s="128" t="s">
+      <c r="I1" s="137" t="s">
         <v>525</v>
       </c>
       <c r="J1" s="144"/>
       <c r="K1" s="144"/>
-      <c r="L1" s="129" t="s">
+      <c r="L1" s="125" t="s">
         <v>575</v>
       </c>
       <c r="M1" s="145"/>
       <c r="N1" s="146"/>
-      <c r="O1" s="132" t="s">
+      <c r="O1" s="128" t="s">
         <v>210</v>
       </c>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
       <c r="R1" s="138"/>
       <c r="S1" s="138"/>
       <c r="T1" s="147"/>
     </row>
     <row r="2" spans="1:20" ht="31.5">
-      <c r="A2" s="125"/>
-      <c r="B2" s="125"/>
+      <c r="A2" s="134"/>
+      <c r="B2" s="134"/>
       <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
@@ -50844,7 +50844,7 @@
       </c>
     </row>
     <row r="52" spans="1:20" ht="18.75">
-      <c r="I52" s="135" t="s">
+      <c r="I52" s="131" t="s">
         <v>370</v>
       </c>
       <c r="J52" s="139"/>
@@ -50878,7 +50878,7 @@
       </c>
     </row>
     <row r="53" spans="1:20" ht="18.75">
-      <c r="I53" s="136" t="s">
+      <c r="I53" s="132" t="s">
         <v>371</v>
       </c>
       <c r="J53" s="140"/>
@@ -50912,7 +50912,7 @@
       </c>
     </row>
     <row r="54" spans="1:20" ht="18.75">
-      <c r="I54" s="137" t="s">
+      <c r="I54" s="133" t="s">
         <v>372</v>
       </c>
       <c r="J54" s="141"/>
@@ -50967,16 +50967,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="I54:K54"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="I54:K54"/>
   </mergeCells>
   <conditionalFormatting sqref="O1:O2">
     <cfRule type="colorScale" priority="11">
@@ -51169,46 +51169,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.75">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="126" t="s">
+      <c r="B1" s="134" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="135" t="s">
         <v>178</v>
       </c>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="127" t="s">
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="136" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="128" t="s">
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="137" t="s">
         <v>525</v>
       </c>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="129" t="s">
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="125" t="s">
         <v>575</v>
       </c>
-      <c r="M1" s="130"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="148" t="s">
+      <c r="M1" s="126"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="159" t="s">
         <v>210</v>
       </c>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="149"/>
+      <c r="P1" s="160"/>
+      <c r="Q1" s="160"/>
+      <c r="R1" s="160"/>
+      <c r="S1" s="160"/>
+      <c r="T1" s="160"/>
+      <c r="U1" s="160"/>
+      <c r="V1" s="160"/>
     </row>
     <row r="2" spans="1:22" ht="31.5">
-      <c r="A2" s="125"/>
-      <c r="B2" s="125"/>
+      <c r="A2" s="134"/>
+      <c r="B2" s="134"/>
       <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
@@ -53866,17 +53866,17 @@
         <v>-3.83</v>
       </c>
       <c r="X36" s="102"/>
-      <c r="Y36" s="153" t="s">
+      <c r="Y36" s="151" t="s">
         <v>688</v>
       </c>
-      <c r="Z36" s="153"/>
-      <c r="AA36" s="153"/>
-      <c r="AB36" s="153"/>
-      <c r="AC36" s="153"/>
-      <c r="AD36" s="153"/>
-      <c r="AE36" s="153"/>
-      <c r="AF36" s="153"/>
-      <c r="AG36" s="153"/>
+      <c r="Z36" s="151"/>
+      <c r="AA36" s="151"/>
+      <c r="AB36" s="151"/>
+      <c r="AC36" s="151"/>
+      <c r="AD36" s="151"/>
+      <c r="AE36" s="151"/>
+      <c r="AF36" s="151"/>
+      <c r="AG36" s="151"/>
       <c r="AH36" s="102"/>
       <c r="AI36" s="102"/>
     </row>
@@ -53956,23 +53956,23 @@
         <v>-1.63</v>
       </c>
       <c r="X37" s="101"/>
-      <c r="Y37" s="160" t="s">
+      <c r="Y37" s="158" t="s">
         <v>687</v>
       </c>
-      <c r="Z37" s="160"/>
-      <c r="AA37" s="157" t="s">
+      <c r="Z37" s="158"/>
+      <c r="AA37" s="155" t="s">
         <v>686</v>
       </c>
-      <c r="AB37" s="157"/>
-      <c r="AC37" s="158" t="s">
+      <c r="AB37" s="155"/>
+      <c r="AC37" s="156" t="s">
         <v>685</v>
       </c>
-      <c r="AD37" s="158"/>
-      <c r="AE37" s="159" t="s">
+      <c r="AD37" s="156"/>
+      <c r="AE37" s="157" t="s">
         <v>684</v>
       </c>
-      <c r="AF37" s="159"/>
-      <c r="AG37" s="159"/>
+      <c r="AF37" s="157"/>
+      <c r="AG37" s="157"/>
       <c r="AH37" s="103"/>
       <c r="AI37" s="103"/>
     </row>
@@ -54052,27 +54052,27 @@
         <v>30.33</v>
       </c>
       <c r="X38" s="91"/>
-      <c r="Y38" s="150">
+      <c r="Y38" s="148">
         <f>E3</f>
         <v>1083.5999999999999</v>
       </c>
-      <c r="Z38" s="151"/>
-      <c r="AA38" s="154">
+      <c r="Z38" s="149"/>
+      <c r="AA38" s="152">
         <f>H3</f>
         <v>413.19</v>
       </c>
-      <c r="AB38" s="155"/>
-      <c r="AC38" s="154">
+      <c r="AB38" s="153"/>
+      <c r="AC38" s="152">
         <f>K3</f>
         <v>88.44</v>
       </c>
-      <c r="AD38" s="155"/>
-      <c r="AE38" s="154">
+      <c r="AD38" s="153"/>
+      <c r="AE38" s="152">
         <f>N3</f>
         <v>22.07</v>
       </c>
-      <c r="AF38" s="155"/>
-      <c r="AG38" s="155"/>
+      <c r="AF38" s="153"/>
+      <c r="AG38" s="153"/>
       <c r="AH38" s="104"/>
       <c r="AI38" s="104"/>
     </row>
@@ -54152,26 +54152,26 @@
         <v>7.07</v>
       </c>
       <c r="X39" s="100"/>
-      <c r="Y39" s="152" t="s">
+      <c r="Y39" s="150" t="s">
         <v>689</v>
       </c>
-      <c r="Z39" s="152"/>
-      <c r="AA39" s="156">
+      <c r="Z39" s="150"/>
+      <c r="AA39" s="154">
         <f>$Y$38/AA38</f>
         <v>2.6225223262905684</v>
       </c>
-      <c r="AB39" s="156"/>
-      <c r="AC39" s="156">
+      <c r="AB39" s="154"/>
+      <c r="AC39" s="154">
         <f>$Y$38/AC38</f>
         <v>12.252374491180461</v>
       </c>
-      <c r="AD39" s="156"/>
-      <c r="AE39" s="156">
+      <c r="AD39" s="154"/>
+      <c r="AE39" s="154">
         <f>$Y$38/AE38</f>
         <v>49.098323516085181</v>
       </c>
-      <c r="AF39" s="156"/>
-      <c r="AG39" s="156"/>
+      <c r="AF39" s="154"/>
+      <c r="AG39" s="154"/>
       <c r="AH39" s="100"/>
       <c r="AI39" s="100"/>
     </row>
@@ -55196,11 +55196,11 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="30.75" customHeight="1">
-      <c r="I52" s="135" t="s">
+      <c r="I52" s="131" t="s">
         <v>370</v>
       </c>
-      <c r="J52" s="135"/>
-      <c r="K52" s="135"/>
+      <c r="J52" s="131"/>
+      <c r="K52" s="131"/>
       <c r="L52" s="37"/>
       <c r="M52" s="52"/>
       <c r="N52" s="52"/>
@@ -55238,11 +55238,11 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="30.75" customHeight="1">
-      <c r="I53" s="136" t="s">
+      <c r="I53" s="132" t="s">
         <v>371</v>
       </c>
-      <c r="J53" s="136"/>
-      <c r="K53" s="136"/>
+      <c r="J53" s="132"/>
+      <c r="K53" s="132"/>
       <c r="L53" s="38"/>
       <c r="M53" s="53"/>
       <c r="N53" s="53"/>
@@ -55280,11 +55280,11 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="30.75" customHeight="1">
-      <c r="I54" s="137" t="s">
+      <c r="I54" s="133" t="s">
         <v>372</v>
       </c>
-      <c r="J54" s="137"/>
-      <c r="K54" s="137"/>
+      <c r="J54" s="133"/>
+      <c r="K54" s="133"/>
       <c r="L54" s="39"/>
       <c r="M54" s="54"/>
       <c r="N54" s="54"/>
@@ -55349,6 +55349,16 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="Y38:Z38"/>
     <mergeCell ref="Y39:Z39"/>
     <mergeCell ref="Y36:AG36"/>
@@ -55362,16 +55372,6 @@
     <mergeCell ref="AC37:AD37"/>
     <mergeCell ref="AE37:AG37"/>
     <mergeCell ref="Y37:Z37"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="O1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="O1:O2">
     <cfRule type="colorScale" priority="18">
@@ -55638,35 +55638,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="127" t="s">
+      <c r="B1" s="134" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="136" t="s">
         <v>377</v>
       </c>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="128" t="s">
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="137" t="s">
         <v>525</v>
       </c>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="129" t="s">
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="125" t="s">
         <v>575</v>
       </c>
-      <c r="J1" s="130"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="133" t="s">
+      <c r="J1" s="126"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="129" t="s">
         <v>210</v>
       </c>
-      <c r="M1" s="134"/>
+      <c r="M1" s="130"/>
     </row>
     <row r="2" spans="1:13" ht="31.5">
-      <c r="A2" s="125"/>
-      <c r="B2" s="125"/>
+      <c r="A2" s="134"/>
+      <c r="B2" s="134"/>
       <c r="C2" s="40" t="s">
         <v>1</v>
       </c>
@@ -57809,11 +57809,11 @@
       </c>
     </row>
     <row r="52" spans="1:13" ht="30.75" customHeight="1">
-      <c r="F52" s="135" t="s">
+      <c r="F52" s="131" t="s">
         <v>370</v>
       </c>
-      <c r="G52" s="135"/>
-      <c r="H52" s="135"/>
+      <c r="G52" s="131"/>
+      <c r="H52" s="131"/>
       <c r="I52" s="37"/>
       <c r="J52" s="52"/>
       <c r="K52" s="52"/>
@@ -57827,11 +57827,11 @@
       </c>
     </row>
     <row r="53" spans="1:13" ht="30.75" customHeight="1">
-      <c r="F53" s="136" t="s">
+      <c r="F53" s="132" t="s">
         <v>371</v>
       </c>
-      <c r="G53" s="136"/>
-      <c r="H53" s="136"/>
+      <c r="G53" s="132"/>
+      <c r="H53" s="132"/>
       <c r="I53" s="38"/>
       <c r="J53" s="53"/>
       <c r="K53" s="53"/>
@@ -57845,11 +57845,11 @@
       </c>
     </row>
     <row r="54" spans="1:13" ht="30.75" customHeight="1">
-      <c r="F54" s="137" t="s">
+      <c r="F54" s="133" t="s">
         <v>372</v>
       </c>
-      <c r="G54" s="137"/>
-      <c r="H54" s="137"/>
+      <c r="G54" s="133"/>
+      <c r="H54" s="133"/>
       <c r="I54" s="39"/>
       <c r="J54" s="54"/>
       <c r="K54" s="54"/>
@@ -57962,46 +57962,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="18.75">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="163" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
       <c r="G1" s="76"/>
       <c r="H1" s="91"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
-      <c r="L1" s="165"/>
-      <c r="M1" s="165"/>
-      <c r="N1" s="165"/>
-      <c r="O1" s="165"/>
-      <c r="P1" s="165"/>
-      <c r="Q1" s="165"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
+      <c r="L1" s="164"/>
+      <c r="M1" s="164"/>
+      <c r="N1" s="164"/>
+      <c r="O1" s="164"/>
+      <c r="P1" s="164"/>
+      <c r="Q1" s="164"/>
     </row>
     <row r="2" spans="1:18" ht="18.75">
-      <c r="A2" s="168"/>
-      <c r="B2" s="168"/>
-      <c r="C2" s="168"/>
-      <c r="D2" s="168"/>
-      <c r="E2" s="168"/>
+      <c r="A2" s="163"/>
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
       <c r="G2" s="76"/>
       <c r="H2" s="113" t="s">
         <v>757</v>
       </c>
-      <c r="I2" s="166" t="s">
+      <c r="I2" s="165" t="s">
         <v>762</v>
       </c>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
-      <c r="L2" s="166"/>
-      <c r="M2" s="166"/>
-      <c r="N2" s="166"/>
-      <c r="O2" s="166"/>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="166"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
+      <c r="L2" s="165"/>
+      <c r="M2" s="165"/>
+      <c r="N2" s="165"/>
+      <c r="O2" s="165"/>
+      <c r="P2" s="165"/>
+      <c r="Q2" s="165"/>
     </row>
     <row r="3" spans="1:18" ht="18.75">
       <c r="A3" s="107" t="s">
@@ -58023,17 +58023,17 @@
       <c r="H3" s="113" t="s">
         <v>758</v>
       </c>
-      <c r="I3" s="166" t="s">
+      <c r="I3" s="165" t="s">
         <v>763</v>
       </c>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
-      <c r="L3" s="166"/>
-      <c r="M3" s="166"/>
-      <c r="N3" s="166"/>
-      <c r="O3" s="166"/>
-      <c r="P3" s="166"/>
-      <c r="Q3" s="166"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
+      <c r="L3" s="165"/>
+      <c r="M3" s="165"/>
+      <c r="N3" s="165"/>
+      <c r="O3" s="165"/>
+      <c r="P3" s="165"/>
+      <c r="Q3" s="165"/>
     </row>
     <row r="4" spans="1:18" ht="45">
       <c r="A4" s="108" t="s">
@@ -58051,20 +58051,20 @@
       <c r="E4" s="70">
         <v>38.06</v>
       </c>
-      <c r="F4" s="162" t="s">
+      <c r="F4" s="166" t="s">
         <v>757</v>
       </c>
       <c r="G4" s="112"/>
       <c r="H4" s="91"/>
-      <c r="I4" s="165"/>
-      <c r="J4" s="165"/>
-      <c r="K4" s="165"/>
-      <c r="L4" s="165"/>
-      <c r="M4" s="165"/>
-      <c r="N4" s="165"/>
-      <c r="O4" s="165"/>
-      <c r="P4" s="165"/>
-      <c r="Q4" s="165"/>
+      <c r="I4" s="164"/>
+      <c r="J4" s="164"/>
+      <c r="K4" s="164"/>
+      <c r="L4" s="164"/>
+      <c r="M4" s="164"/>
+      <c r="N4" s="164"/>
+      <c r="O4" s="164"/>
+      <c r="P4" s="164"/>
+      <c r="Q4" s="164"/>
     </row>
     <row r="5" spans="1:18" ht="45">
       <c r="A5" s="108" t="s">
@@ -58082,18 +58082,18 @@
       <c r="E5" s="70">
         <v>21.1</v>
       </c>
-      <c r="F5" s="163"/>
+      <c r="F5" s="167"/>
       <c r="G5" s="112"/>
       <c r="H5" s="91"/>
-      <c r="I5" s="165"/>
-      <c r="J5" s="165"/>
-      <c r="K5" s="165"/>
-      <c r="L5" s="165"/>
-      <c r="M5" s="165"/>
-      <c r="N5" s="165"/>
-      <c r="O5" s="165"/>
-      <c r="P5" s="165"/>
-      <c r="Q5" s="165"/>
+      <c r="I5" s="164"/>
+      <c r="J5" s="164"/>
+      <c r="K5" s="164"/>
+      <c r="L5" s="164"/>
+      <c r="M5" s="164"/>
+      <c r="N5" s="164"/>
+      <c r="O5" s="164"/>
+      <c r="P5" s="164"/>
+      <c r="Q5" s="164"/>
     </row>
     <row r="6" spans="1:18" ht="45">
       <c r="A6" s="108" t="s">
@@ -58111,21 +58111,21 @@
       <c r="E6" s="70">
         <v>18.7</v>
       </c>
-      <c r="F6" s="163"/>
+      <c r="F6" s="167"/>
       <c r="G6" s="112"/>
-      <c r="H6" s="167" t="s">
+      <c r="H6" s="162" t="s">
         <v>761</v>
       </c>
-      <c r="I6" s="167"/>
-      <c r="J6" s="167"/>
-      <c r="K6" s="167"/>
-      <c r="L6" s="167"/>
-      <c r="M6" s="167"/>
-      <c r="N6" s="167"/>
-      <c r="O6" s="167"/>
-      <c r="P6" s="167"/>
-      <c r="Q6" s="167"/>
-      <c r="R6" s="167"/>
+      <c r="I6" s="162"/>
+      <c r="J6" s="162"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="162"/>
+      <c r="Q6" s="162"/>
+      <c r="R6" s="162"/>
     </row>
     <row r="7" spans="1:18" ht="45">
       <c r="A7" s="108" t="s">
@@ -58143,29 +58143,29 @@
       <c r="E7" s="70">
         <v>8.99</v>
       </c>
-      <c r="F7" s="163"/>
+      <c r="F7" s="167"/>
       <c r="G7" s="112"/>
       <c r="H7" s="122"/>
-      <c r="I7" s="164">
+      <c r="I7" s="161">
         <v>20</v>
       </c>
-      <c r="J7" s="164"/>
-      <c r="K7" s="164">
+      <c r="J7" s="161"/>
+      <c r="K7" s="161">
         <v>21</v>
       </c>
-      <c r="L7" s="164"/>
-      <c r="M7" s="164">
+      <c r="L7" s="161"/>
+      <c r="M7" s="161">
         <v>22</v>
       </c>
-      <c r="N7" s="164"/>
-      <c r="O7" s="164">
+      <c r="N7" s="161"/>
+      <c r="O7" s="161">
         <v>23</v>
       </c>
-      <c r="P7" s="164"/>
-      <c r="Q7" s="164">
+      <c r="P7" s="161"/>
+      <c r="Q7" s="161">
         <v>24</v>
       </c>
-      <c r="R7" s="164"/>
+      <c r="R7" s="161"/>
     </row>
     <row r="8" spans="1:18" ht="45">
       <c r="A8" s="108" t="s">
@@ -58183,7 +58183,7 @@
       <c r="E8" s="70">
         <v>0.96</v>
       </c>
-      <c r="F8" s="163"/>
+      <c r="F8" s="167"/>
       <c r="G8" s="112"/>
       <c r="H8" s="105" t="s">
         <v>756</v>
@@ -58235,7 +58235,7 @@
       <c r="E9" s="70">
         <v>1</v>
       </c>
-      <c r="F9" s="163"/>
+      <c r="F9" s="167"/>
       <c r="G9" s="112"/>
       <c r="H9" s="105">
         <v>1</v>
@@ -58283,7 +58283,7 @@
       <c r="E10" s="70">
         <v>1.3</v>
       </c>
-      <c r="F10" s="163"/>
+      <c r="F10" s="167"/>
       <c r="G10" s="112"/>
       <c r="H10" s="105">
         <v>2</v>
@@ -58331,7 +58331,7 @@
       <c r="E11" s="116">
         <v>69.87</v>
       </c>
-      <c r="F11" s="162" t="s">
+      <c r="F11" s="166" t="s">
         <v>758</v>
       </c>
       <c r="H11" s="105">
@@ -58380,7 +58380,7 @@
       <c r="E12" s="116">
         <v>36.119999999999997</v>
       </c>
-      <c r="F12" s="163"/>
+      <c r="F12" s="167"/>
       <c r="H12" s="105">
         <v>4</v>
       </c>
@@ -58427,7 +58427,7 @@
       <c r="E13" s="116">
         <v>38.89</v>
       </c>
-      <c r="F13" s="163"/>
+      <c r="F13" s="167"/>
       <c r="H13" s="98">
         <v>5</v>
       </c>
@@ -58488,7 +58488,7 @@
       <c r="E14" s="116">
         <v>20.6</v>
       </c>
-      <c r="F14" s="163"/>
+      <c r="F14" s="167"/>
     </row>
     <row r="15" spans="1:18" ht="45">
       <c r="A15" s="120" t="s">
@@ -58506,21 +58506,21 @@
       <c r="E15" s="116">
         <v>5.87</v>
       </c>
-      <c r="F15" s="163"/>
+      <c r="F15" s="167"/>
       <c r="H15" s="123">
         <v>1</v>
       </c>
-      <c r="I15" s="161" t="s">
+      <c r="I15" s="168" t="s">
         <v>678</v>
       </c>
-      <c r="J15" s="161"/>
-      <c r="K15" s="161"/>
-      <c r="L15" s="161"/>
-      <c r="M15" s="161"/>
-      <c r="N15" s="161"/>
-      <c r="O15" s="161"/>
-      <c r="P15" s="161"/>
-      <c r="Q15" s="161"/>
+      <c r="J15" s="168"/>
+      <c r="K15" s="168"/>
+      <c r="L15" s="168"/>
+      <c r="M15" s="168"/>
+      <c r="N15" s="168"/>
+      <c r="O15" s="168"/>
+      <c r="P15" s="168"/>
+      <c r="Q15" s="168"/>
     </row>
     <row r="16" spans="1:18" ht="45">
       <c r="A16" s="120" t="s">
@@ -58538,21 +58538,21 @@
       <c r="E16" s="116">
         <v>6.09</v>
       </c>
-      <c r="F16" s="163"/>
+      <c r="F16" s="167"/>
       <c r="H16" s="123">
         <v>2</v>
       </c>
-      <c r="I16" s="161" t="s">
+      <c r="I16" s="168" t="s">
         <v>677</v>
       </c>
-      <c r="J16" s="161"/>
-      <c r="K16" s="161"/>
-      <c r="L16" s="161"/>
-      <c r="M16" s="161"/>
-      <c r="N16" s="161"/>
-      <c r="O16" s="161"/>
-      <c r="P16" s="161"/>
-      <c r="Q16" s="161"/>
+      <c r="J16" s="168"/>
+      <c r="K16" s="168"/>
+      <c r="L16" s="168"/>
+      <c r="M16" s="168"/>
+      <c r="N16" s="168"/>
+      <c r="O16" s="168"/>
+      <c r="P16" s="168"/>
+      <c r="Q16" s="168"/>
     </row>
     <row r="17" spans="1:17" ht="45">
       <c r="A17" s="120" t="s">
@@ -58570,56 +58570,65 @@
       <c r="E17" s="116">
         <v>6.42</v>
       </c>
-      <c r="F17" s="163"/>
+      <c r="F17" s="167"/>
       <c r="H17" s="123">
         <v>3</v>
       </c>
-      <c r="I17" s="161" t="s">
+      <c r="I17" s="168" t="s">
         <v>679</v>
       </c>
-      <c r="J17" s="161"/>
-      <c r="K17" s="161"/>
-      <c r="L17" s="161"/>
-      <c r="M17" s="161"/>
-      <c r="N17" s="161"/>
-      <c r="O17" s="161"/>
-      <c r="P17" s="161"/>
-      <c r="Q17" s="161"/>
+      <c r="J17" s="168"/>
+      <c r="K17" s="168"/>
+      <c r="L17" s="168"/>
+      <c r="M17" s="168"/>
+      <c r="N17" s="168"/>
+      <c r="O17" s="168"/>
+      <c r="P17" s="168"/>
+      <c r="Q17" s="168"/>
     </row>
     <row r="18" spans="1:17" ht="18.75">
       <c r="H18" s="123">
         <v>4</v>
       </c>
-      <c r="I18" s="161" t="s">
+      <c r="I18" s="168" t="s">
         <v>680</v>
       </c>
-      <c r="J18" s="161"/>
-      <c r="K18" s="161"/>
-      <c r="L18" s="161"/>
-      <c r="M18" s="161"/>
-      <c r="N18" s="161"/>
-      <c r="O18" s="161"/>
-      <c r="P18" s="161"/>
-      <c r="Q18" s="161"/>
+      <c r="J18" s="168"/>
+      <c r="K18" s="168"/>
+      <c r="L18" s="168"/>
+      <c r="M18" s="168"/>
+      <c r="N18" s="168"/>
+      <c r="O18" s="168"/>
+      <c r="P18" s="168"/>
+      <c r="Q18" s="168"/>
     </row>
     <row r="19" spans="1:17" ht="18.75">
       <c r="H19" s="123">
         <v>5</v>
       </c>
-      <c r="I19" s="161" t="s">
+      <c r="I19" s="168" t="s">
         <v>681</v>
       </c>
-      <c r="J19" s="161"/>
-      <c r="K19" s="161"/>
-      <c r="L19" s="161"/>
-      <c r="M19" s="161"/>
-      <c r="N19" s="161"/>
-      <c r="O19" s="161"/>
-      <c r="P19" s="161"/>
-      <c r="Q19" s="161"/>
+      <c r="J19" s="168"/>
+      <c r="K19" s="168"/>
+      <c r="L19" s="168"/>
+      <c r="M19" s="168"/>
+      <c r="N19" s="168"/>
+      <c r="O19" s="168"/>
+      <c r="P19" s="168"/>
+      <c r="Q19" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I18:Q18"/>
+    <mergeCell ref="I19:Q19"/>
+    <mergeCell ref="F11:F17"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="I15:Q15"/>
+    <mergeCell ref="I16:Q16"/>
+    <mergeCell ref="I17:Q17"/>
     <mergeCell ref="Q7:R7"/>
     <mergeCell ref="H6:R6"/>
     <mergeCell ref="I7:J7"/>
@@ -58630,15 +58639,6 @@
     <mergeCell ref="I4:Q4"/>
     <mergeCell ref="I5:Q5"/>
     <mergeCell ref="F4:F10"/>
-    <mergeCell ref="F11:F17"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="I15:Q15"/>
-    <mergeCell ref="I16:Q16"/>
-    <mergeCell ref="I17:Q17"/>
-    <mergeCell ref="I18:Q18"/>
-    <mergeCell ref="I19:Q19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -58661,62 +58661,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="21.75" thickBot="1">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="176" t="s">
         <v>682</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="L1" s="169" t="s">
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="L1" s="173" t="s">
         <v>629</v>
       </c>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="170"/>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="170"/>
-      <c r="R1" s="170"/>
-      <c r="S1" s="170"/>
-      <c r="T1" s="170"/>
-      <c r="U1" s="170"/>
-      <c r="V1" s="171"/>
-      <c r="X1" s="169" t="s">
+      <c r="M1" s="174"/>
+      <c r="N1" s="174"/>
+      <c r="O1" s="174"/>
+      <c r="P1" s="174"/>
+      <c r="Q1" s="174"/>
+      <c r="R1" s="174"/>
+      <c r="S1" s="174"/>
+      <c r="T1" s="174"/>
+      <c r="U1" s="174"/>
+      <c r="V1" s="175"/>
+      <c r="X1" s="173" t="s">
         <v>631</v>
       </c>
-      <c r="Y1" s="170"/>
-      <c r="Z1" s="170"/>
-      <c r="AA1" s="170"/>
-      <c r="AB1" s="170"/>
-      <c r="AC1" s="170"/>
-      <c r="AD1" s="170"/>
-      <c r="AE1" s="170"/>
-      <c r="AF1" s="170"/>
-      <c r="AG1" s="170"/>
-      <c r="AH1" s="171"/>
+      <c r="Y1" s="174"/>
+      <c r="Z1" s="174"/>
+      <c r="AA1" s="174"/>
+      <c r="AB1" s="174"/>
+      <c r="AC1" s="174"/>
+      <c r="AD1" s="174"/>
+      <c r="AE1" s="174"/>
+      <c r="AF1" s="174"/>
+      <c r="AG1" s="174"/>
+      <c r="AH1" s="175"/>
     </row>
     <row r="2" spans="1:34" ht="36.75" customHeight="1">
       <c r="A2" s="61"/>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="136" t="s">
         <v>614</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="128" t="s">
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="137" t="s">
         <v>617</v>
       </c>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="173" t="s">
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="177" t="s">
         <v>618</v>
       </c>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
+      <c r="I2" s="177"/>
+      <c r="J2" s="177"/>
       <c r="L2" s="75"/>
       <c r="M2" s="76"/>
       <c r="N2" s="76"/>
@@ -59206,18 +59206,18 @@
       <c r="AH11" s="77"/>
     </row>
     <row r="12" spans="1:34" ht="21">
-      <c r="A12" s="172" t="s">
+      <c r="A12" s="176" t="s">
         <v>621</v>
       </c>
-      <c r="B12" s="172"/>
-      <c r="C12" s="172"/>
-      <c r="D12" s="172"/>
-      <c r="E12" s="172"/>
-      <c r="F12" s="172"/>
-      <c r="G12" s="172"/>
-      <c r="H12" s="172"/>
-      <c r="I12" s="172"/>
-      <c r="J12" s="172"/>
+      <c r="B12" s="176"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="176"/>
+      <c r="J12" s="176"/>
       <c r="L12" s="75"/>
       <c r="M12" s="76"/>
       <c r="N12" s="76"/>
@@ -59243,21 +59243,21 @@
     </row>
     <row r="13" spans="1:34" ht="35.25" customHeight="1">
       <c r="A13" s="61"/>
-      <c r="B13" s="127" t="s">
+      <c r="B13" s="136" t="s">
         <v>614</v>
       </c>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="128" t="s">
+      <c r="C13" s="136"/>
+      <c r="D13" s="136"/>
+      <c r="E13" s="137" t="s">
         <v>617</v>
       </c>
-      <c r="F13" s="128"/>
-      <c r="G13" s="128"/>
-      <c r="H13" s="173" t="s">
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="177" t="s">
         <v>618</v>
       </c>
-      <c r="I13" s="173"/>
-      <c r="J13" s="173"/>
+      <c r="I13" s="177"/>
+      <c r="J13" s="177"/>
       <c r="L13" s="75"/>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
@@ -59526,19 +59526,19 @@
         <f>'15 Elementos'!T54</f>
         <v>1.1399999999999999</v>
       </c>
-      <c r="L18" s="169" t="s">
+      <c r="L18" s="173" t="s">
         <v>630</v>
       </c>
-      <c r="M18" s="170"/>
-      <c r="N18" s="170"/>
-      <c r="O18" s="170"/>
-      <c r="P18" s="170"/>
-      <c r="Q18" s="170"/>
-      <c r="R18" s="170"/>
-      <c r="S18" s="170"/>
-      <c r="T18" s="170"/>
-      <c r="U18" s="170"/>
-      <c r="V18" s="171"/>
+      <c r="M18" s="174"/>
+      <c r="N18" s="174"/>
+      <c r="O18" s="174"/>
+      <c r="P18" s="174"/>
+      <c r="Q18" s="174"/>
+      <c r="R18" s="174"/>
+      <c r="S18" s="174"/>
+      <c r="T18" s="174"/>
+      <c r="U18" s="174"/>
+      <c r="V18" s="175"/>
       <c r="X18" s="75"/>
       <c r="Y18" s="76"/>
       <c r="Z18" s="76"/>
@@ -59886,19 +59886,19 @@
       <c r="A27" s="94" t="s">
         <v>676</v>
       </c>
-      <c r="B27" s="157" t="s">
+      <c r="B27" s="155" t="s">
         <v>686</v>
       </c>
-      <c r="C27" s="157"/>
-      <c r="D27" s="174" t="s">
+      <c r="C27" s="155"/>
+      <c r="D27" s="178" t="s">
         <v>685</v>
       </c>
-      <c r="E27" s="175"/>
-      <c r="F27" s="159" t="s">
+      <c r="E27" s="179"/>
+      <c r="F27" s="157" t="s">
         <v>684</v>
       </c>
-      <c r="G27" s="159"/>
-      <c r="H27" s="159"/>
+      <c r="G27" s="157"/>
+      <c r="H27" s="157"/>
       <c r="I27" s="95" t="s">
         <v>529</v>
       </c>
@@ -59932,19 +59932,19 @@
       <c r="A28" s="90">
         <v>1</v>
       </c>
-      <c r="B28" s="161">
+      <c r="B28" s="168">
         <v>0.35</v>
       </c>
-      <c r="C28" s="161"/>
-      <c r="D28" s="176">
+      <c r="C28" s="168"/>
+      <c r="D28" s="169">
         <v>0.33</v>
       </c>
-      <c r="E28" s="177"/>
-      <c r="F28" s="161">
+      <c r="E28" s="170"/>
+      <c r="F28" s="168">
         <v>0.27</v>
       </c>
-      <c r="G28" s="161"/>
-      <c r="H28" s="161"/>
+      <c r="G28" s="168"/>
+      <c r="H28" s="168"/>
       <c r="I28" s="99">
         <f>B28/D28</f>
         <v>1.0606060606060606</v>
@@ -59980,19 +59980,19 @@
       <c r="A29" s="90">
         <v>2</v>
       </c>
-      <c r="B29" s="161">
+      <c r="B29" s="168">
         <v>829.35</v>
       </c>
-      <c r="C29" s="161"/>
-      <c r="D29" s="176">
+      <c r="C29" s="168"/>
+      <c r="D29" s="169">
         <v>148.22</v>
       </c>
-      <c r="E29" s="177"/>
-      <c r="F29" s="161">
+      <c r="E29" s="170"/>
+      <c r="F29" s="168">
         <v>4.28</v>
       </c>
-      <c r="G29" s="161"/>
-      <c r="H29" s="161"/>
+      <c r="G29" s="168"/>
+      <c r="H29" s="168"/>
       <c r="I29" s="99">
         <f t="shared" ref="I29:I31" si="2">B29/D29</f>
         <v>5.595398731615167</v>
@@ -60028,19 +60028,19 @@
       <c r="A30" s="90">
         <v>3</v>
       </c>
-      <c r="B30" s="161">
+      <c r="B30" s="168">
         <v>14.05</v>
       </c>
-      <c r="C30" s="161"/>
-      <c r="D30" s="176">
+      <c r="C30" s="168"/>
+      <c r="D30" s="169">
         <v>20.03</v>
       </c>
-      <c r="E30" s="177"/>
-      <c r="F30" s="161">
+      <c r="E30" s="170"/>
+      <c r="F30" s="168">
         <v>13.32</v>
       </c>
-      <c r="G30" s="161"/>
-      <c r="H30" s="161"/>
+      <c r="G30" s="168"/>
+      <c r="H30" s="168"/>
       <c r="I30" s="99">
         <f t="shared" si="2"/>
         <v>0.70144782825761354</v>
@@ -60076,19 +60076,19 @@
       <c r="A31" s="90">
         <v>4</v>
       </c>
-      <c r="B31" s="161">
+      <c r="B31" s="168">
         <v>0.23</v>
       </c>
-      <c r="C31" s="161"/>
-      <c r="D31" s="161">
+      <c r="C31" s="168"/>
+      <c r="D31" s="168">
         <v>22.95</v>
       </c>
-      <c r="E31" s="161"/>
-      <c r="F31" s="161">
+      <c r="E31" s="168"/>
+      <c r="F31" s="168">
         <v>23.72</v>
       </c>
-      <c r="G31" s="161"/>
-      <c r="H31" s="161"/>
+      <c r="G31" s="168"/>
+      <c r="H31" s="168"/>
       <c r="I31" s="99">
         <f t="shared" si="2"/>
         <v>1.0021786492374729E-2</v>
@@ -60124,22 +60124,22 @@
       <c r="A32" s="93">
         <v>5</v>
       </c>
-      <c r="B32" s="179">
+      <c r="B32" s="172">
         <f>SUM(B28:C31)</f>
         <v>843.98</v>
       </c>
-      <c r="C32" s="179"/>
-      <c r="D32" s="179">
+      <c r="C32" s="172"/>
+      <c r="D32" s="172">
         <f>SUM(D28:E31)</f>
         <v>191.53</v>
       </c>
-      <c r="E32" s="179"/>
-      <c r="F32" s="179">
+      <c r="E32" s="172"/>
+      <c r="F32" s="172">
         <f>SUM(F28:H31)</f>
         <v>41.59</v>
       </c>
-      <c r="G32" s="179"/>
-      <c r="H32" s="179"/>
+      <c r="G32" s="172"/>
+      <c r="H32" s="172"/>
       <c r="I32" s="73">
         <f>B32/D32</f>
         <v>4.4065159505038372</v>
@@ -60199,17 +60199,17 @@
       <c r="A34" s="92">
         <v>1</v>
       </c>
-      <c r="B34" s="178" t="s">
+      <c r="B34" s="171" t="s">
         <v>678</v>
       </c>
-      <c r="C34" s="178"/>
-      <c r="D34" s="178"/>
-      <c r="E34" s="178"/>
-      <c r="F34" s="178"/>
-      <c r="G34" s="178"/>
-      <c r="H34" s="178"/>
-      <c r="I34" s="178"/>
-      <c r="J34" s="178"/>
+      <c r="C34" s="171"/>
+      <c r="D34" s="171"/>
+      <c r="E34" s="171"/>
+      <c r="F34" s="171"/>
+      <c r="G34" s="171"/>
+      <c r="H34" s="171"/>
+      <c r="I34" s="171"/>
+      <c r="J34" s="171"/>
       <c r="L34" s="75"/>
       <c r="M34" s="76"/>
       <c r="N34" s="76"/>
@@ -60237,17 +60237,17 @@
       <c r="A35" s="92">
         <v>2</v>
       </c>
-      <c r="B35" s="178" t="s">
+      <c r="B35" s="171" t="s">
         <v>677</v>
       </c>
-      <c r="C35" s="178"/>
-      <c r="D35" s="178"/>
-      <c r="E35" s="178"/>
-      <c r="F35" s="178"/>
-      <c r="G35" s="178"/>
-      <c r="H35" s="178"/>
-      <c r="I35" s="178"/>
-      <c r="J35" s="178"/>
+      <c r="C35" s="171"/>
+      <c r="D35" s="171"/>
+      <c r="E35" s="171"/>
+      <c r="F35" s="171"/>
+      <c r="G35" s="171"/>
+      <c r="H35" s="171"/>
+      <c r="I35" s="171"/>
+      <c r="J35" s="171"/>
       <c r="L35" s="75"/>
       <c r="M35" s="76"/>
       <c r="N35" s="76"/>
@@ -60264,17 +60264,17 @@
       <c r="A36" s="92">
         <v>3</v>
       </c>
-      <c r="B36" s="178" t="s">
+      <c r="B36" s="171" t="s">
         <v>679</v>
       </c>
-      <c r="C36" s="178"/>
-      <c r="D36" s="178"/>
-      <c r="E36" s="178"/>
-      <c r="F36" s="178"/>
-      <c r="G36" s="178"/>
-      <c r="H36" s="178"/>
-      <c r="I36" s="178"/>
-      <c r="J36" s="178"/>
+      <c r="C36" s="171"/>
+      <c r="D36" s="171"/>
+      <c r="E36" s="171"/>
+      <c r="F36" s="171"/>
+      <c r="G36" s="171"/>
+      <c r="H36" s="171"/>
+      <c r="I36" s="171"/>
+      <c r="J36" s="171"/>
       <c r="L36" s="75"/>
       <c r="M36" s="76"/>
       <c r="N36" s="76"/>
@@ -60291,17 +60291,17 @@
       <c r="A37" s="92">
         <v>4</v>
       </c>
-      <c r="B37" s="178" t="s">
+      <c r="B37" s="171" t="s">
         <v>680</v>
       </c>
-      <c r="C37" s="178"/>
-      <c r="D37" s="178"/>
-      <c r="E37" s="178"/>
-      <c r="F37" s="178"/>
-      <c r="G37" s="178"/>
-      <c r="H37" s="178"/>
-      <c r="I37" s="178"/>
-      <c r="J37" s="178"/>
+      <c r="C37" s="171"/>
+      <c r="D37" s="171"/>
+      <c r="E37" s="171"/>
+      <c r="F37" s="171"/>
+      <c r="G37" s="171"/>
+      <c r="H37" s="171"/>
+      <c r="I37" s="171"/>
+      <c r="J37" s="171"/>
       <c r="L37" s="75"/>
       <c r="M37" s="76"/>
       <c r="N37" s="76"/>
@@ -60318,17 +60318,17 @@
       <c r="A38" s="92">
         <v>5</v>
       </c>
-      <c r="B38" s="178" t="s">
+      <c r="B38" s="171" t="s">
         <v>681</v>
       </c>
-      <c r="C38" s="178"/>
-      <c r="D38" s="178"/>
-      <c r="E38" s="178"/>
-      <c r="F38" s="178"/>
-      <c r="G38" s="178"/>
-      <c r="H38" s="178"/>
-      <c r="I38" s="178"/>
-      <c r="J38" s="178"/>
+      <c r="C38" s="171"/>
+      <c r="D38" s="171"/>
+      <c r="E38" s="171"/>
+      <c r="F38" s="171"/>
+      <c r="G38" s="171"/>
+      <c r="H38" s="171"/>
+      <c r="I38" s="171"/>
+      <c r="J38" s="171"/>
       <c r="L38" s="75"/>
       <c r="M38" s="76"/>
       <c r="N38" s="76"/>
@@ -60640,25 +60640,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="B38:J38"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B37:J37"/>
     <mergeCell ref="X1:AH1"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
@@ -60675,6 +60656,25 @@
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="A25:J26"/>
+    <mergeCell ref="B38:J38"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
